--- a/frontend/public/reports/StockPulse_ESCOLAR.xlsx
+++ b/frontend/public/reports/StockPulse_ESCOLAR.xlsx
@@ -37,10 +37,10 @@
     <t>U. x Caja</t>
   </si>
   <si>
-    <t>Stock VES</t>
-  </si>
-  <si>
-    <t>Alerta</t>
+    <t>Stock</t>
+  </si>
+  <si>
+    <t>Estado</t>
   </si>
   <si>
     <t>2210</t>
@@ -52,7 +52,7 @@
     <t>FORRO N VINIFAN OFICIO CRISTAL 26</t>
   </si>
   <si>
-    <t>🟢</t>
+    <t>✓ OK</t>
   </si>
   <si>
     <t>2211</t>
@@ -73,7 +73,7 @@
     <t>FORRO N VINIFANCITO CRISTAL 26</t>
   </si>
   <si>
-    <t>🔴</t>
+    <t>✗ AGOTADO</t>
   </si>
   <si>
     <t>2182</t>
@@ -136,7 +136,7 @@
     <t>PORTAPAPELES VINIFAN OFICIO X 10 UND - 2013</t>
   </si>
   <si>
-    <t>🟡</t>
+    <t>⚠ BAJO</t>
   </si>
   <si>
     <t>78455</t>
@@ -4223,7 +4223,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -4237,6 +4237,22 @@
     </font>
     <font>
       <b/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF065F46"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFDC2626"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFD97706"/>
+      <sz val="12"/>
     </font>
   </fonts>
   <fills count="6">
@@ -4279,7 +4295,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4287,13 +4303,19 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -4638,13 +4660,12 @@
   <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="55" customWidth="1"/>
-    <col min="5" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="8" customWidth="1"/>
+    <col min="4" max="4" width="45" customWidth="1"/>
+    <col min="5" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -4758,7 +4779,7 @@
       <c r="F5" s="4">
         <v>0</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -4981,13 +5002,12 @@
   <dimension ref="A1:G31"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="55" customWidth="1"/>
-    <col min="5" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="8" customWidth="1"/>
+    <col min="4" max="4" width="45" customWidth="1"/>
+    <col min="5" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -5216,7 +5236,7 @@
       <c r="F10" s="4">
         <v>0</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="G10" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -5538,7 +5558,7 @@
       <c r="F24" s="4">
         <v>0</v>
       </c>
-      <c r="G24" s="3" t="s">
+      <c r="G24" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -5561,7 +5581,7 @@
       <c r="F25" s="4">
         <v>0</v>
       </c>
-      <c r="G25" s="3" t="s">
+      <c r="G25" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -5607,7 +5627,7 @@
       <c r="F27" s="4">
         <v>0</v>
       </c>
-      <c r="G27" s="3" t="s">
+      <c r="G27" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -5676,7 +5696,7 @@
       <c r="F30" s="4">
         <v>0</v>
       </c>
-      <c r="G30" s="3" t="s">
+      <c r="G30" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -5715,13 +5735,12 @@
   <dimension ref="A1:G266"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="55" customWidth="1"/>
-    <col min="5" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="8" customWidth="1"/>
+    <col min="4" max="4" width="45" customWidth="1"/>
+    <col min="5" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -5763,10 +5782,10 @@
       <c r="E2">
         <v>50</v>
       </c>
-      <c r="F2" s="5">
+      <c r="F2" s="6">
         <v>1</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -5809,10 +5828,10 @@
       <c r="E4">
         <v>50</v>
       </c>
-      <c r="F4" s="5">
+      <c r="F4" s="6">
         <v>2</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -5901,10 +5920,10 @@
       <c r="E8">
         <v>50</v>
       </c>
-      <c r="F8" s="5">
-        <v>8</v>
-      </c>
-      <c r="G8" s="3" t="s">
+      <c r="F8" s="6">
+        <v>8</v>
+      </c>
+      <c r="G8" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -6177,10 +6196,10 @@
       <c r="E20">
         <v>50</v>
       </c>
-      <c r="F20" s="5">
+      <c r="F20" s="6">
         <v>6</v>
       </c>
-      <c r="G20" s="3" t="s">
+      <c r="G20" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -6571,7 +6590,7 @@
       <c r="F37" s="4">
         <v>0</v>
       </c>
-      <c r="G37" s="3" t="s">
+      <c r="G37" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -6683,10 +6702,10 @@
       <c r="E42">
         <v>100</v>
       </c>
-      <c r="F42" s="5">
+      <c r="F42" s="6">
         <v>9</v>
       </c>
-      <c r="G42" s="3" t="s">
+      <c r="G42" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -6709,7 +6728,7 @@
       <c r="F43" s="4">
         <v>0</v>
       </c>
-      <c r="G43" s="3" t="s">
+      <c r="G43" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -7215,7 +7234,7 @@
       <c r="F65" s="4">
         <v>0</v>
       </c>
-      <c r="G65" s="3" t="s">
+      <c r="G65" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -7603,10 +7622,10 @@
       <c r="E82">
         <v>100</v>
       </c>
-      <c r="F82" s="5">
+      <c r="F82" s="6">
         <v>9</v>
       </c>
-      <c r="G82" s="3" t="s">
+      <c r="G82" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -8040,10 +8059,10 @@
       <c r="E101">
         <v>120</v>
       </c>
-      <c r="F101" s="5">
+      <c r="F101" s="6">
         <v>6</v>
       </c>
-      <c r="G101" s="3" t="s">
+      <c r="G101" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -8270,10 +8289,10 @@
       <c r="E111">
         <v>120</v>
       </c>
-      <c r="F111" s="5">
-        <v>8</v>
-      </c>
-      <c r="G111" s="3" t="s">
+      <c r="F111" s="6">
+        <v>8</v>
+      </c>
+      <c r="G111" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -8365,7 +8384,7 @@
       <c r="F115" s="4">
         <v>0</v>
       </c>
-      <c r="G115" s="3" t="s">
+      <c r="G115" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -8385,10 +8404,10 @@
       <c r="E116">
         <v>24</v>
       </c>
-      <c r="F116" s="5">
+      <c r="F116" s="6">
         <v>3</v>
       </c>
-      <c r="G116" s="3" t="s">
+      <c r="G116" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -8408,10 +8427,10 @@
       <c r="E117">
         <v>24</v>
       </c>
-      <c r="F117" s="5">
+      <c r="F117" s="6">
         <v>1</v>
       </c>
-      <c r="G117" s="3" t="s">
+      <c r="G117" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -8618,7 +8637,7 @@
       <c r="F126" s="4">
         <v>0</v>
       </c>
-      <c r="G126" s="3" t="s">
+      <c r="G126" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -8779,7 +8798,7 @@
       <c r="F133" s="4">
         <v>0</v>
       </c>
-      <c r="G133" s="3" t="s">
+      <c r="G133" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -8825,7 +8844,7 @@
       <c r="F135" s="4">
         <v>0</v>
       </c>
-      <c r="G135" s="3" t="s">
+      <c r="G135" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -8871,7 +8890,7 @@
       <c r="F137" s="4">
         <v>0</v>
       </c>
-      <c r="G137" s="3" t="s">
+      <c r="G137" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -8894,7 +8913,7 @@
       <c r="F138" s="4">
         <v>0</v>
       </c>
-      <c r="G138" s="3" t="s">
+      <c r="G138" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -8986,7 +9005,7 @@
       <c r="F142" s="4">
         <v>0</v>
       </c>
-      <c r="G142" s="3" t="s">
+      <c r="G142" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -9006,10 +9025,10 @@
       <c r="E143">
         <v>24</v>
       </c>
-      <c r="F143" s="5">
+      <c r="F143" s="6">
         <v>3</v>
       </c>
-      <c r="G143" s="3" t="s">
+      <c r="G143" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -9032,7 +9051,7 @@
       <c r="F144" s="4">
         <v>0</v>
       </c>
-      <c r="G144" s="3" t="s">
+      <c r="G144" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -9075,10 +9094,10 @@
       <c r="E146">
         <v>24</v>
       </c>
-      <c r="F146" s="5">
+      <c r="F146" s="6">
         <v>5</v>
       </c>
-      <c r="G146" s="3" t="s">
+      <c r="G146" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -9098,10 +9117,10 @@
       <c r="E147">
         <v>24</v>
       </c>
-      <c r="F147" s="5">
+      <c r="F147" s="6">
         <v>4</v>
       </c>
-      <c r="G147" s="3" t="s">
+      <c r="G147" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -9400,7 +9419,7 @@
       <c r="F160" s="4">
         <v>0</v>
       </c>
-      <c r="G160" s="3" t="s">
+      <c r="G160" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -9535,10 +9554,10 @@
       <c r="E166">
         <v>24</v>
       </c>
-      <c r="F166" s="5">
+      <c r="F166" s="6">
         <v>1</v>
       </c>
-      <c r="G166" s="3" t="s">
+      <c r="G166" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -9627,10 +9646,10 @@
       <c r="E170">
         <v>36</v>
       </c>
-      <c r="F170" s="5">
+      <c r="F170" s="6">
         <v>3</v>
       </c>
-      <c r="G170" s="3" t="s">
+      <c r="G170" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -9653,7 +9672,7 @@
       <c r="F171" s="4">
         <v>0</v>
       </c>
-      <c r="G171" s="3" t="s">
+      <c r="G171" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -9676,7 +9695,7 @@
       <c r="F172" s="4">
         <v>0</v>
       </c>
-      <c r="G172" s="3" t="s">
+      <c r="G172" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -9745,7 +9764,7 @@
       <c r="F175" s="4">
         <v>0</v>
       </c>
-      <c r="G175" s="3" t="s">
+      <c r="G175" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -9860,7 +9879,7 @@
       <c r="F180" s="4">
         <v>0</v>
       </c>
-      <c r="G180" s="3" t="s">
+      <c r="G180" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -9883,7 +9902,7 @@
       <c r="F181" s="4">
         <v>0</v>
       </c>
-      <c r="G181" s="3" t="s">
+      <c r="G181" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -10113,7 +10132,7 @@
       <c r="F191" s="4">
         <v>0</v>
       </c>
-      <c r="G191" s="3" t="s">
+      <c r="G191" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -10136,7 +10155,7 @@
       <c r="F192" s="4">
         <v>0</v>
       </c>
-      <c r="G192" s="3" t="s">
+      <c r="G192" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -10228,7 +10247,7 @@
       <c r="F196" s="4">
         <v>0</v>
       </c>
-      <c r="G196" s="3" t="s">
+      <c r="G196" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -10251,7 +10270,7 @@
       <c r="F197" s="4">
         <v>0</v>
       </c>
-      <c r="G197" s="3" t="s">
+      <c r="G197" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -10550,7 +10569,7 @@
       <c r="F210" s="4">
         <v>0</v>
       </c>
-      <c r="G210" s="3" t="s">
+      <c r="G210" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -10754,10 +10773,10 @@
       <c r="E219">
         <v>5</v>
       </c>
-      <c r="F219" s="5">
+      <c r="F219" s="6">
         <v>1</v>
       </c>
-      <c r="G219" s="3" t="s">
+      <c r="G219" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -10780,7 +10799,7 @@
       <c r="F220" s="4">
         <v>0</v>
       </c>
-      <c r="G220" s="3" t="s">
+      <c r="G220" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -10964,7 +10983,7 @@
       <c r="F228" s="4">
         <v>0</v>
       </c>
-      <c r="G228" s="3" t="s">
+      <c r="G228" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -11033,7 +11052,7 @@
       <c r="F231" s="4">
         <v>0</v>
       </c>
-      <c r="G231" s="3" t="s">
+      <c r="G231" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -11283,10 +11302,10 @@
       <c r="E242">
         <v>5</v>
       </c>
-      <c r="F242" s="5">
+      <c r="F242" s="6">
         <v>1</v>
       </c>
-      <c r="G242" s="3" t="s">
+      <c r="G242" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -11355,7 +11374,7 @@
       <c r="F245" s="4">
         <v>0</v>
       </c>
-      <c r="G245" s="3" t="s">
+      <c r="G245" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -11444,10 +11463,10 @@
       <c r="E249">
         <v>5</v>
       </c>
-      <c r="F249" s="5">
+      <c r="F249" s="6">
         <v>1</v>
       </c>
-      <c r="G249" s="3" t="s">
+      <c r="G249" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -11516,7 +11535,7 @@
       <c r="F252" s="4">
         <v>0</v>
       </c>
-      <c r="G252" s="3" t="s">
+      <c r="G252" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -11539,7 +11558,7 @@
       <c r="F253" s="4">
         <v>0</v>
       </c>
-      <c r="G253" s="3" t="s">
+      <c r="G253" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -11854,13 +11873,12 @@
   <dimension ref="A1:G77"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="55" customWidth="1"/>
-    <col min="5" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="8" customWidth="1"/>
+    <col min="4" max="4" width="45" customWidth="1"/>
+    <col min="5" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -11928,7 +11946,7 @@
       <c r="F3" s="4">
         <v>0</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -11951,7 +11969,7 @@
       <c r="F4" s="4">
         <v>0</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -12066,7 +12084,7 @@
       <c r="F9" s="4">
         <v>0</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="G9" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -12319,7 +12337,7 @@
       <c r="F20" s="4">
         <v>0</v>
       </c>
-      <c r="G20" s="3" t="s">
+      <c r="G20" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -12342,7 +12360,7 @@
       <c r="F21" s="4">
         <v>0</v>
       </c>
-      <c r="G21" s="3" t="s">
+      <c r="G21" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -12848,7 +12866,7 @@
       <c r="F43" s="4">
         <v>0</v>
       </c>
-      <c r="G43" s="3" t="s">
+      <c r="G43" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -13259,10 +13277,10 @@
       <c r="E61">
         <v>12</v>
       </c>
-      <c r="F61" s="5">
+      <c r="F61" s="6">
         <v>1</v>
       </c>
-      <c r="G61" s="3" t="s">
+      <c r="G61" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -13285,7 +13303,7 @@
       <c r="F62" s="4">
         <v>0</v>
       </c>
-      <c r="G62" s="3" t="s">
+      <c r="G62" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -13305,10 +13323,10 @@
       <c r="E63">
         <v>12</v>
       </c>
-      <c r="F63" s="5">
+      <c r="F63" s="6">
         <v>4</v>
       </c>
-      <c r="G63" s="3" t="s">
+      <c r="G63" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -13328,10 +13346,10 @@
       <c r="E64">
         <v>12</v>
       </c>
-      <c r="F64" s="5">
+      <c r="F64" s="6">
         <v>9</v>
       </c>
-      <c r="G64" s="3" t="s">
+      <c r="G64" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -13351,10 +13369,10 @@
       <c r="E65">
         <v>12</v>
       </c>
-      <c r="F65" s="5">
+      <c r="F65" s="6">
         <v>3</v>
       </c>
-      <c r="G65" s="3" t="s">
+      <c r="G65" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -13400,7 +13418,7 @@
       <c r="F67" s="4">
         <v>0</v>
       </c>
-      <c r="G67" s="3" t="s">
+      <c r="G67" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -13423,7 +13441,7 @@
       <c r="F68" s="4">
         <v>0</v>
       </c>
-      <c r="G68" s="3" t="s">
+      <c r="G68" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -13446,7 +13464,7 @@
       <c r="F69" s="4">
         <v>0</v>
       </c>
-      <c r="G69" s="3" t="s">
+      <c r="G69" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -13469,7 +13487,7 @@
       <c r="F70" s="4">
         <v>0</v>
       </c>
-      <c r="G70" s="3" t="s">
+      <c r="G70" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -13492,7 +13510,7 @@
       <c r="F71" s="4">
         <v>0</v>
       </c>
-      <c r="G71" s="3" t="s">
+      <c r="G71" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -13646,13 +13664,12 @@
   <dimension ref="A1:G144"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="55" customWidth="1"/>
-    <col min="5" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="8" customWidth="1"/>
+    <col min="4" max="4" width="45" customWidth="1"/>
+    <col min="5" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -14177,10 +14194,10 @@
       <c r="E23">
         <v>192</v>
       </c>
-      <c r="F23" s="5">
+      <c r="F23" s="6">
         <v>3</v>
       </c>
-      <c r="G23" s="3" t="s">
+      <c r="G23" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -14430,10 +14447,10 @@
       <c r="E34">
         <v>72</v>
       </c>
-      <c r="F34" s="5">
+      <c r="F34" s="6">
         <v>6</v>
       </c>
-      <c r="G34" s="3" t="s">
+      <c r="G34" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -14660,10 +14677,10 @@
       <c r="E44">
         <v>72</v>
       </c>
-      <c r="F44" s="5">
+      <c r="F44" s="6">
         <v>2</v>
       </c>
-      <c r="G44" s="3" t="s">
+      <c r="G44" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -15054,7 +15071,7 @@
       <c r="F61" s="4">
         <v>0</v>
       </c>
-      <c r="G61" s="3" t="s">
+      <c r="G61" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -15120,10 +15137,10 @@
       <c r="E64">
         <v>200</v>
       </c>
-      <c r="F64" s="5">
+      <c r="F64" s="6">
         <v>5</v>
       </c>
-      <c r="G64" s="3" t="s">
+      <c r="G64" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -15304,10 +15321,10 @@
       <c r="E72">
         <v>200</v>
       </c>
-      <c r="F72" s="5">
+      <c r="F72" s="6">
         <v>5</v>
       </c>
-      <c r="G72" s="3" t="s">
+      <c r="G72" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -15330,7 +15347,7 @@
       <c r="F73" s="4">
         <v>0</v>
       </c>
-      <c r="G73" s="3" t="s">
+      <c r="G73" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -15376,7 +15393,7 @@
       <c r="F75" s="4">
         <v>0</v>
       </c>
-      <c r="G75" s="3" t="s">
+      <c r="G75" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -15422,7 +15439,7 @@
       <c r="F77" s="4">
         <v>0</v>
       </c>
-      <c r="G77" s="3" t="s">
+      <c r="G77" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -15445,7 +15462,7 @@
       <c r="F78" s="4">
         <v>0</v>
       </c>
-      <c r="G78" s="3" t="s">
+      <c r="G78" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -15488,10 +15505,10 @@
       <c r="E80">
         <v>200</v>
       </c>
-      <c r="F80" s="5">
+      <c r="F80" s="6">
         <v>3</v>
       </c>
-      <c r="G80" s="3" t="s">
+      <c r="G80" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -15514,7 +15531,7 @@
       <c r="F81" s="4">
         <v>0</v>
       </c>
-      <c r="G81" s="3" t="s">
+      <c r="G81" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -15580,10 +15597,10 @@
       <c r="E84">
         <v>1152</v>
       </c>
-      <c r="F84" s="5">
+      <c r="F84" s="6">
         <v>7</v>
       </c>
-      <c r="G84" s="3" t="s">
+      <c r="G84" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -15741,10 +15758,10 @@
       <c r="E91">
         <v>576</v>
       </c>
-      <c r="F91" s="5">
+      <c r="F91" s="6">
         <v>3</v>
       </c>
-      <c r="G91" s="3" t="s">
+      <c r="G91" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -15810,10 +15827,10 @@
       <c r="E94">
         <v>576</v>
       </c>
-      <c r="F94" s="5">
+      <c r="F94" s="6">
         <v>4</v>
       </c>
-      <c r="G94" s="3" t="s">
+      <c r="G94" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -15836,7 +15853,7 @@
       <c r="F95" s="4">
         <v>0</v>
       </c>
-      <c r="G95" s="3" t="s">
+      <c r="G95" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -15928,7 +15945,7 @@
       <c r="F99" s="4">
         <v>0</v>
       </c>
-      <c r="G99" s="3" t="s">
+      <c r="G99" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -15971,10 +15988,10 @@
       <c r="E101">
         <v>144</v>
       </c>
-      <c r="F101" s="5">
+      <c r="F101" s="6">
         <v>2</v>
       </c>
-      <c r="G101" s="3" t="s">
+      <c r="G101" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -16089,7 +16106,7 @@
       <c r="F106" s="4">
         <v>0</v>
       </c>
-      <c r="G106" s="3" t="s">
+      <c r="G106" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -16388,7 +16405,7 @@
       <c r="F119" s="4">
         <v>0</v>
       </c>
-      <c r="G119" s="3" t="s">
+      <c r="G119" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -16979,13 +16996,12 @@
   <dimension ref="A1:G96"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="55" customWidth="1"/>
-    <col min="5" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="8" customWidth="1"/>
+    <col min="4" max="4" width="45" customWidth="1"/>
+    <col min="5" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -17030,7 +17046,7 @@
       <c r="F2" s="4">
         <v>0</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -17145,7 +17161,7 @@
       <c r="F7" s="4">
         <v>0</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="G7" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -17283,7 +17299,7 @@
       <c r="F13" s="4">
         <v>0</v>
       </c>
-      <c r="G13" s="3" t="s">
+      <c r="G13" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -17329,7 +17345,7 @@
       <c r="F15" s="4">
         <v>0</v>
       </c>
-      <c r="G15" s="3" t="s">
+      <c r="G15" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -17349,10 +17365,10 @@
       <c r="E16">
         <v>24</v>
       </c>
-      <c r="F16" s="5">
+      <c r="F16" s="6">
         <v>3</v>
       </c>
-      <c r="G16" s="3" t="s">
+      <c r="G16" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -17375,7 +17391,7 @@
       <c r="F17" s="4">
         <v>0</v>
       </c>
-      <c r="G17" s="3" t="s">
+      <c r="G17" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -17398,7 +17414,7 @@
       <c r="F18" s="4">
         <v>0</v>
       </c>
-      <c r="G18" s="3" t="s">
+      <c r="G18" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -17605,7 +17621,7 @@
       <c r="F27" s="4">
         <v>0</v>
       </c>
-      <c r="G27" s="3" t="s">
+      <c r="G27" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -17720,7 +17736,7 @@
       <c r="F32" s="4">
         <v>0</v>
       </c>
-      <c r="G32" s="3" t="s">
+      <c r="G32" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -18226,7 +18242,7 @@
       <c r="F54" s="4">
         <v>0</v>
       </c>
-      <c r="G54" s="3" t="s">
+      <c r="G54" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -18249,7 +18265,7 @@
       <c r="F55" s="4">
         <v>0</v>
       </c>
-      <c r="G55" s="3" t="s">
+      <c r="G55" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -18295,7 +18311,7 @@
       <c r="F57" s="4">
         <v>0</v>
       </c>
-      <c r="G57" s="3" t="s">
+      <c r="G57" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -18318,7 +18334,7 @@
       <c r="F58" s="4">
         <v>0</v>
       </c>
-      <c r="G58" s="3" t="s">
+      <c r="G58" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -18410,7 +18426,7 @@
       <c r="F62" s="4">
         <v>0</v>
       </c>
-      <c r="G62" s="3" t="s">
+      <c r="G62" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -18476,10 +18492,10 @@
       <c r="E65">
         <v>12</v>
       </c>
-      <c r="F65" s="5">
+      <c r="F65" s="6">
         <v>5</v>
       </c>
-      <c r="G65" s="3" t="s">
+      <c r="G65" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -18545,10 +18561,10 @@
       <c r="E68">
         <v>12</v>
       </c>
-      <c r="F68" s="5">
+      <c r="F68" s="6">
         <v>4</v>
       </c>
-      <c r="G68" s="3" t="s">
+      <c r="G68" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -18617,7 +18633,7 @@
       <c r="F71" s="4">
         <v>0</v>
       </c>
-      <c r="G71" s="3" t="s">
+      <c r="G71" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -18640,7 +18656,7 @@
       <c r="F72" s="4">
         <v>0</v>
       </c>
-      <c r="G72" s="3" t="s">
+      <c r="G72" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -18729,10 +18745,10 @@
       <c r="E76">
         <v>180</v>
       </c>
-      <c r="F76" s="5">
+      <c r="F76" s="6">
         <v>4</v>
       </c>
-      <c r="G76" s="3" t="s">
+      <c r="G76" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -18824,7 +18840,7 @@
       <c r="F80" s="4">
         <v>0</v>
       </c>
-      <c r="G80" s="3" t="s">
+      <c r="G80" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -18939,7 +18955,7 @@
       <c r="F85" s="4">
         <v>0</v>
       </c>
-      <c r="G85" s="3" t="s">
+      <c r="G85" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -19097,10 +19113,10 @@
       <c r="E92">
         <v>144</v>
       </c>
-      <c r="F92" s="5">
+      <c r="F92" s="6">
         <v>4</v>
       </c>
-      <c r="G92" s="3" t="s">
+      <c r="G92" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -19143,10 +19159,10 @@
       <c r="E94">
         <v>144</v>
       </c>
-      <c r="F94" s="5">
+      <c r="F94" s="6">
         <v>3</v>
       </c>
-      <c r="G94" s="3" t="s">
+      <c r="G94" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -19169,7 +19185,7 @@
       <c r="F95" s="4">
         <v>0</v>
       </c>
-      <c r="G95" s="3" t="s">
+      <c r="G95" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -19208,13 +19224,12 @@
   <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="55" customWidth="1"/>
-    <col min="5" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="8" customWidth="1"/>
+    <col min="4" max="4" width="45" customWidth="1"/>
+    <col min="5" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -19344,13 +19359,12 @@
   <dimension ref="A1:G32"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="55" customWidth="1"/>
-    <col min="5" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="8" customWidth="1"/>
+    <col min="4" max="4" width="45" customWidth="1"/>
+    <col min="5" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -20082,10 +20096,10 @@
       <c r="E32">
         <v>48</v>
       </c>
-      <c r="F32" s="5">
+      <c r="F32" s="6">
         <v>2</v>
       </c>
-      <c r="G32" s="3" t="s">
+      <c r="G32" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -20101,13 +20115,12 @@
   <dimension ref="A1:G22"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="55" customWidth="1"/>
-    <col min="5" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="8" customWidth="1"/>
+    <col min="4" max="4" width="45" customWidth="1"/>
+    <col min="5" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -20333,10 +20346,10 @@
       <c r="E10">
         <v>36</v>
       </c>
-      <c r="F10" s="5">
+      <c r="F10" s="6">
         <v>2</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="G10" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -20359,7 +20372,7 @@
       <c r="F11" s="4">
         <v>0</v>
       </c>
-      <c r="G11" s="3" t="s">
+      <c r="G11" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -20494,10 +20507,10 @@
       <c r="E17">
         <v>72</v>
       </c>
-      <c r="F17" s="5">
+      <c r="F17" s="6">
         <v>1</v>
       </c>
-      <c r="G17" s="3" t="s">
+      <c r="G17" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -20586,10 +20599,10 @@
       <c r="E21">
         <v>144</v>
       </c>
-      <c r="F21" s="5">
+      <c r="F21" s="6">
         <v>6</v>
       </c>
-      <c r="G21" s="3" t="s">
+      <c r="G21" s="7" t="s">
         <v>38</v>
       </c>
     </row>
@@ -20628,13 +20641,12 @@
   <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="55" customWidth="1"/>
-    <col min="5" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="8" customWidth="1"/>
+    <col min="4" max="4" width="45" customWidth="1"/>
+    <col min="5" max="6" width="10" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -20863,7 +20875,7 @@
       <c r="F10" s="4">
         <v>0</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="G10" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -20886,7 +20898,7 @@
       <c r="F11" s="4">
         <v>0</v>
       </c>
-      <c r="G11" s="3" t="s">
+      <c r="G11" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -20929,10 +20941,10 @@
       <c r="E13">
         <v>500</v>
       </c>
-      <c r="F13" s="5">
+      <c r="F13" s="6">
         <v>5</v>
       </c>
-      <c r="G13" s="3" t="s">
+      <c r="G13" s="7" t="s">
         <v>38</v>
       </c>
     </row>

--- a/frontend/public/reports/StockPulse_ESCOLAR.xlsx
+++ b/frontend/public/reports/StockPulse_ESCOLAR.xlsx
@@ -7518,11 +7518,11 @@
       <c r="E23">
         <v>300</v>
       </c>
-      <c r="F23" s="6">
+      <c r="F23" s="2">
         <v>1775</v>
       </c>
-      <c r="G23" s="7" t="s">
-        <v>49</v>
+      <c r="G23" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -8044,11 +8044,11 @@
       <c r="E14">
         <v>50</v>
       </c>
-      <c r="F14" s="6">
+      <c r="F14" s="2">
         <v>471</v>
       </c>
-      <c r="G14" s="7" t="s">
-        <v>49</v>
+      <c r="G14" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -8067,11 +8067,11 @@
       <c r="E15">
         <v>50</v>
       </c>
-      <c r="F15" s="6">
+      <c r="F15" s="2">
         <v>445</v>
       </c>
-      <c r="G15" s="7" t="s">
-        <v>49</v>
+      <c r="G15" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -8964,11 +8964,11 @@
       <c r="E54">
         <v>100</v>
       </c>
-      <c r="F54" s="6">
+      <c r="F54" s="2">
         <v>751</v>
       </c>
-      <c r="G54" s="7" t="s">
-        <v>49</v>
+      <c r="G54" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
@@ -9102,11 +9102,11 @@
       <c r="E60">
         <v>100</v>
       </c>
-      <c r="F60" s="6">
+      <c r="F60" s="2">
         <v>645</v>
       </c>
-      <c r="G60" s="7" t="s">
-        <v>49</v>
+      <c r="G60" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
@@ -9838,11 +9838,11 @@
       <c r="E92">
         <v>100</v>
       </c>
-      <c r="F92" s="6">
+      <c r="F92" s="2">
         <v>940</v>
       </c>
-      <c r="G92" s="7" t="s">
-        <v>49</v>
+      <c r="G92" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
@@ -10344,11 +10344,11 @@
       <c r="E114">
         <v>24</v>
       </c>
-      <c r="F114" s="6">
+      <c r="F114" s="2">
         <v>137</v>
       </c>
-      <c r="G114" s="7" t="s">
-        <v>49</v>
+      <c r="G114" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.25">
@@ -10942,11 +10942,11 @@
       <c r="E140">
         <v>30</v>
       </c>
-      <c r="F140" s="6">
+      <c r="F140" s="2">
         <v>297</v>
       </c>
-      <c r="G140" s="7" t="s">
-        <v>49</v>
+      <c r="G140" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
@@ -10965,11 +10965,11 @@
       <c r="E141">
         <v>30</v>
       </c>
-      <c r="F141" s="6">
+      <c r="F141" s="2">
         <v>180</v>
       </c>
-      <c r="G141" s="7" t="s">
-        <v>49</v>
+      <c r="G141" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
@@ -11379,11 +11379,11 @@
       <c r="E159">
         <v>24</v>
       </c>
-      <c r="F159" s="6">
+      <c r="F159" s="2">
         <v>130</v>
       </c>
-      <c r="G159" s="7" t="s">
-        <v>49</v>
+      <c r="G159" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.25">
@@ -11839,11 +11839,11 @@
       <c r="E179">
         <v>36</v>
       </c>
-      <c r="F179" s="6">
+      <c r="F179" s="2">
         <v>218</v>
       </c>
-      <c r="G179" s="7" t="s">
-        <v>49</v>
+      <c r="G179" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.25">
@@ -12299,11 +12299,11 @@
       <c r="E199">
         <v>10</v>
       </c>
-      <c r="F199" s="6">
+      <c r="F199" s="2">
         <v>69</v>
       </c>
-      <c r="G199" s="7" t="s">
-        <v>49</v>
+      <c r="G199" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.25">
@@ -12506,11 +12506,11 @@
       <c r="E208">
         <v>720</v>
       </c>
-      <c r="F208" s="6">
+      <c r="F208" s="2">
         <v>5462</v>
       </c>
-      <c r="G208" s="7" t="s">
-        <v>49</v>
+      <c r="G208" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.25">
@@ -12529,11 +12529,11 @@
       <c r="E209">
         <v>720</v>
       </c>
-      <c r="F209" s="6">
+      <c r="F209" s="2">
         <v>6036</v>
       </c>
-      <c r="G209" s="7" t="s">
-        <v>49</v>
+      <c r="G209" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.25">
@@ -12598,11 +12598,11 @@
       <c r="E212">
         <v>720</v>
       </c>
-      <c r="F212" s="6">
+      <c r="F212" s="2">
         <v>4603</v>
       </c>
-      <c r="G212" s="7" t="s">
-        <v>49</v>
+      <c r="G212" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.25">
@@ -12644,11 +12644,11 @@
       <c r="E214">
         <v>720</v>
       </c>
-      <c r="F214" s="6">
+      <c r="F214" s="2">
         <v>3947</v>
       </c>
-      <c r="G214" s="7" t="s">
-        <v>49</v>
+      <c r="G214" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.25">
@@ -13817,11 +13817,11 @@
       <c r="E265">
         <v>5</v>
       </c>
-      <c r="F265" s="6">
+      <c r="F265" s="2">
         <v>27</v>
       </c>
-      <c r="G265" s="7" t="s">
-        <v>49</v>
+      <c r="G265" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="266" spans="1:7" x14ac:dyDescent="0.25">
@@ -13840,11 +13840,11 @@
       <c r="E266">
         <v>5</v>
       </c>
-      <c r="F266" s="6">
+      <c r="F266" s="2">
         <v>26</v>
       </c>
-      <c r="G266" s="7" t="s">
-        <v>49</v>
+      <c r="G266" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -13998,11 +13998,11 @@
       <c r="E6">
         <v>18</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6" s="2">
         <v>115</v>
       </c>
-      <c r="G6" s="7" t="s">
-        <v>49</v>
+      <c r="G6" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -16157,11 +16157,11 @@
       <c r="E22">
         <v>192</v>
       </c>
-      <c r="F22" s="6">
+      <c r="F22" s="2">
         <v>1033</v>
       </c>
-      <c r="G22" s="7" t="s">
-        <v>49</v>
+      <c r="G22" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -16410,11 +16410,11 @@
       <c r="E33">
         <v>144</v>
       </c>
-      <c r="F33" s="6">
+      <c r="F33" s="2">
         <v>1001</v>
       </c>
-      <c r="G33" s="7" t="s">
-        <v>49</v>
+      <c r="G33" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -16548,11 +16548,11 @@
       <c r="E39">
         <v>144</v>
       </c>
-      <c r="F39" s="6">
+      <c r="F39" s="2">
         <v>1014</v>
       </c>
-      <c r="G39" s="7" t="s">
-        <v>49</v>
+      <c r="G39" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
@@ -16732,11 +16732,11 @@
       <c r="E47">
         <v>144</v>
       </c>
-      <c r="F47" s="6">
+      <c r="F47" s="2">
         <v>1400</v>
       </c>
-      <c r="G47" s="7" t="s">
-        <v>49</v>
+      <c r="G47" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
@@ -17284,11 +17284,11 @@
       <c r="E71">
         <v>200</v>
       </c>
-      <c r="F71" s="6">
+      <c r="F71" s="2">
         <v>1246</v>
       </c>
-      <c r="G71" s="7" t="s">
-        <v>49</v>
+      <c r="G71" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
@@ -17468,11 +17468,11 @@
       <c r="E79">
         <v>200</v>
       </c>
-      <c r="F79" s="6">
+      <c r="F79" s="2">
         <v>1865</v>
       </c>
-      <c r="G79" s="7" t="s">
-        <v>49</v>
+      <c r="G79" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
@@ -17652,11 +17652,11 @@
       <c r="E87">
         <v>576</v>
       </c>
-      <c r="F87" s="6">
+      <c r="F87" s="2">
         <v>4143</v>
       </c>
-      <c r="G87" s="7" t="s">
-        <v>49</v>
+      <c r="G87" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
@@ -17675,11 +17675,11 @@
       <c r="E88">
         <v>576</v>
       </c>
-      <c r="F88" s="6">
+      <c r="F88" s="2">
         <v>5653</v>
       </c>
-      <c r="G88" s="7" t="s">
-        <v>49</v>
+      <c r="G88" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
@@ -17767,11 +17767,11 @@
       <c r="E92">
         <v>576</v>
       </c>
-      <c r="F92" s="6">
+      <c r="F92" s="2">
         <v>5395</v>
       </c>
-      <c r="G92" s="7" t="s">
-        <v>49</v>
+      <c r="G92" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
@@ -18181,11 +18181,11 @@
       <c r="E110">
         <v>192</v>
       </c>
-      <c r="F110" s="6">
+      <c r="F110" s="2">
         <v>1359</v>
       </c>
-      <c r="G110" s="7" t="s">
-        <v>49</v>
+      <c r="G110" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.25">
@@ -20777,11 +20777,11 @@
       <c r="E78">
         <v>144</v>
       </c>
-      <c r="F78" s="6">
+      <c r="F78" s="2">
         <v>936</v>
       </c>
-      <c r="G78" s="7" t="s">
-        <v>49</v>
+      <c r="G78" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.25">
@@ -20984,11 +20984,11 @@
       <c r="E87">
         <v>144</v>
       </c>
-      <c r="F87" s="6">
+      <c r="F87" s="2">
         <v>808</v>
       </c>
-      <c r="G87" s="7" t="s">
-        <v>49</v>
+      <c r="G87" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
@@ -21944,11 +21944,11 @@
       <c r="E26">
         <v>24</v>
       </c>
-      <c r="F26" s="6">
+      <c r="F26" s="2">
         <v>202</v>
       </c>
-      <c r="G26" s="7" t="s">
-        <v>49</v>
+      <c r="G26" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -21967,11 +21967,11 @@
       <c r="E27">
         <v>24</v>
       </c>
-      <c r="F27" s="6">
+      <c r="F27" s="2">
         <v>198</v>
       </c>
-      <c r="G27" s="7" t="s">
-        <v>49</v>
+      <c r="G27" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -22950,11 +22950,11 @@
       <c r="E14">
         <v>200</v>
       </c>
-      <c r="F14" s="6">
+      <c r="F14" s="2">
         <v>1904</v>
       </c>
-      <c r="G14" s="7" t="s">
-        <v>49</v>
+      <c r="G14" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -22973,11 +22973,11 @@
       <c r="E15">
         <v>120</v>
       </c>
-      <c r="F15" s="6">
+      <c r="F15" s="2">
         <v>1063</v>
       </c>
-      <c r="G15" s="7" t="s">
-        <v>49</v>
+      <c r="G15" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">

--- a/frontend/public/reports/StockPulse_ESCOLAR.xlsx
+++ b/frontend/public/reports/StockPulse_ESCOLAR.xlsx
@@ -6786,7 +6786,7 @@
         <v>25</v>
       </c>
       <c r="F6" s="2">
-        <v>3927</v>
+        <v>3627</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>10</v>
@@ -6924,7 +6924,7 @@
         <v>25</v>
       </c>
       <c r="F12" s="2">
-        <v>25578</v>
+        <v>25453</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>10</v>
@@ -14965,7 +14965,7 @@
         <v>144</v>
       </c>
       <c r="F48" s="2">
-        <v>49384</v>
+        <v>49096</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>10</v>
@@ -19927,7 +19927,7 @@
         <v>144</v>
       </c>
       <c r="F41" s="2">
-        <v>7902</v>
+        <v>7758</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>10</v>
@@ -21393,7 +21393,7 @@
         <v>12</v>
       </c>
       <c r="F2" s="2">
-        <v>1184</v>
+        <v>1172</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -21462,7 +21462,7 @@
         <v>12</v>
       </c>
       <c r="F5" s="2">
-        <v>874</v>
+        <v>862</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>

--- a/frontend/public/reports/StockPulse_ESCOLAR.xlsx
+++ b/frontend/public/reports/StockPulse_ESCOLAR.xlsx
@@ -6787,7 +6787,7 @@
         <v>25</v>
       </c>
       <c r="F6" s="2">
-        <v>3927</v>
+        <v>3627</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>10</v>
@@ -6925,7 +6925,7 @@
         <v>25</v>
       </c>
       <c r="F12" s="2">
-        <v>25578</v>
+        <v>25453</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>10</v>
@@ -14966,7 +14966,7 @@
         <v>144</v>
       </c>
       <c r="F48" s="2">
-        <v>49384</v>
+        <v>49096</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>10</v>
@@ -19928,7 +19928,7 @@
         <v>144</v>
       </c>
       <c r="F41" s="2">
-        <v>7902</v>
+        <v>7758</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>10</v>
@@ -21394,7 +21394,7 @@
         <v>12</v>
       </c>
       <c r="F2" s="2">
-        <v>1184</v>
+        <v>1172</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -21463,7 +21463,7 @@
         <v>12</v>
       </c>
       <c r="F5" s="2">
-        <v>874</v>
+        <v>862</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>

--- a/frontend/public/reports/StockPulse_ESCOLAR.xlsx
+++ b/frontend/public/reports/StockPulse_ESCOLAR.xlsx
@@ -14046,7 +14046,7 @@
         <v>72</v>
       </c>
       <c r="F8" s="2">
-        <v>15579</v>
+        <v>15578</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>10</v>
@@ -14276,7 +14276,7 @@
         <v>72</v>
       </c>
       <c r="F18" s="2">
-        <v>8012</v>
+        <v>8011</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>10</v>
@@ -14391,7 +14391,7 @@
         <v>60</v>
       </c>
       <c r="F23" s="2">
-        <v>13509</v>
+        <v>13508</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>10</v>
@@ -14989,7 +14989,7 @@
         <v>36</v>
       </c>
       <c r="F49" s="2">
-        <v>38451</v>
+        <v>38450</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>10</v>
@@ -15722,7 +15722,7 @@
         <v>144</v>
       </c>
       <c r="F3" s="2">
-        <v>37794</v>
+        <v>37793</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -16205,7 +16205,7 @@
         <v>96</v>
       </c>
       <c r="F24" s="2">
-        <v>3512</v>
+        <v>3511</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>10</v>
@@ -19928,7 +19928,7 @@
         <v>144</v>
       </c>
       <c r="F41" s="2">
-        <v>7743</v>
+        <v>7742</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>10</v>
@@ -22472,7 +22472,7 @@
         <v>48</v>
       </c>
       <c r="F16" s="2">
-        <v>16218</v>
+        <v>16216</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>10</v>
@@ -22837,7 +22837,7 @@
         <v>200</v>
       </c>
       <c r="F9" s="2">
-        <v>40774</v>
+        <v>40773</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>10</v>
@@ -22998,7 +22998,7 @@
         <v>200</v>
       </c>
       <c r="F16" s="2">
-        <v>2948</v>
+        <v>2947</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>10</v>

--- a/frontend/public/reports/StockPulse_ESCOLAR.xlsx
+++ b/frontend/public/reports/StockPulse_ESCOLAR.xlsx
@@ -7793,7 +7793,7 @@
         <v>50</v>
       </c>
       <c r="F3" s="2">
-        <v>46870</v>
+        <v>46970</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -7862,7 +7862,7 @@
         <v>50</v>
       </c>
       <c r="F6" s="2">
-        <v>18563</v>
+        <v>17813</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>10</v>
@@ -7931,7 +7931,7 @@
         <v>50</v>
       </c>
       <c r="F9" s="2">
-        <v>3743</v>
+        <v>3643</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>10</v>
@@ -7977,7 +7977,7 @@
         <v>50</v>
       </c>
       <c r="F11" s="2">
-        <v>5110</v>
+        <v>5010</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>10</v>
@@ -8000,7 +8000,7 @@
         <v>50</v>
       </c>
       <c r="F12" s="2">
-        <v>3109</v>
+        <v>3009</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>10</v>
@@ -8023,7 +8023,7 @@
         <v>50</v>
       </c>
       <c r="F13" s="2">
-        <v>4475</v>
+        <v>4375</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>10</v>
@@ -8045,11 +8045,11 @@
       <c r="E14">
         <v>50</v>
       </c>
-      <c r="F14" s="2">
-        <v>271</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>10</v>
+      <c r="F14" s="6">
+        <v>171</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -8069,7 +8069,7 @@
         <v>50</v>
       </c>
       <c r="F15" s="2">
-        <v>395</v>
+        <v>295</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>10</v>
@@ -8092,7 +8092,7 @@
         <v>50</v>
       </c>
       <c r="F16" s="2">
-        <v>5117</v>
+        <v>5017</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>10</v>
@@ -8115,7 +8115,7 @@
         <v>50</v>
       </c>
       <c r="F17" s="2">
-        <v>8232</v>
+        <v>8132</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>10</v>
@@ -8138,7 +8138,7 @@
         <v>50</v>
       </c>
       <c r="F18" s="2">
-        <v>15719</v>
+        <v>15619</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>10</v>
@@ -8161,7 +8161,7 @@
         <v>50</v>
       </c>
       <c r="F19" s="2">
-        <v>2347</v>
+        <v>2247</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>10</v>
@@ -8207,7 +8207,7 @@
         <v>50</v>
       </c>
       <c r="F21" s="2">
-        <v>750</v>
+        <v>650</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>10</v>
@@ -8230,7 +8230,7 @@
         <v>50</v>
       </c>
       <c r="F22" s="2">
-        <v>743</v>
+        <v>643</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>10</v>
@@ -14046,7 +14046,7 @@
         <v>72</v>
       </c>
       <c r="F8" s="2">
-        <v>15505</v>
+        <v>15289</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>10</v>
@@ -14115,7 +14115,7 @@
         <v>144</v>
       </c>
       <c r="F11" s="2">
-        <v>53217</v>
+        <v>52785</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>10</v>
@@ -14414,7 +14414,7 @@
         <v>48</v>
       </c>
       <c r="F24" s="2">
-        <v>12442</v>
+        <v>12202</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>10</v>
@@ -14989,7 +14989,7 @@
         <v>36</v>
       </c>
       <c r="F49" s="2">
-        <v>37693</v>
+        <v>37845</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>10</v>
@@ -17861,7 +17861,7 @@
         <v>144</v>
       </c>
       <c r="F96" s="2">
-        <v>189582</v>
+        <v>190794</v>
       </c>
       <c r="G96" s="3" t="s">
         <v>10</v>
@@ -18965,7 +18965,7 @@
         <v>192</v>
       </c>
       <c r="F144" s="6">
-        <v>58</v>
+        <v>258</v>
       </c>
       <c r="G144" s="7" t="s">
         <v>49</v>
@@ -19928,7 +19928,7 @@
         <v>144</v>
       </c>
       <c r="F41" s="2">
-        <v>7442</v>
+        <v>7394</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>10</v>
@@ -20066,7 +20066,7 @@
         <v>144</v>
       </c>
       <c r="F47" s="2">
-        <v>4054</v>
+        <v>4006</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>10</v>
@@ -20089,7 +20089,7 @@
         <v>144</v>
       </c>
       <c r="F48" s="2">
-        <v>10180</v>
+        <v>10132</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>10</v>
@@ -20112,7 +20112,7 @@
         <v>144</v>
       </c>
       <c r="F49" s="2">
-        <v>15509</v>
+        <v>15461</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>10</v>
@@ -20135,7 +20135,7 @@
         <v>144</v>
       </c>
       <c r="F50" s="2">
-        <v>5656</v>
+        <v>5608</v>
       </c>
       <c r="G50" s="3" t="s">
         <v>10</v>
@@ -20158,7 +20158,7 @@
         <v>144</v>
       </c>
       <c r="F51" s="2">
-        <v>5151</v>
+        <v>5079</v>
       </c>
       <c r="G51" s="3" t="s">
         <v>10</v>
@@ -20181,7 +20181,7 @@
         <v>144</v>
       </c>
       <c r="F52" s="2">
-        <v>6526</v>
+        <v>6454</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>10</v>
@@ -20204,7 +20204,7 @@
         <v>144</v>
       </c>
       <c r="F53" s="2">
-        <v>6337</v>
+        <v>6289</v>
       </c>
       <c r="G53" s="3" t="s">
         <v>10</v>
@@ -21259,7 +21259,7 @@
         <v>72</v>
       </c>
       <c r="F2" s="2">
-        <v>120176</v>
+        <v>120032</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -21282,7 +21282,7 @@
         <v>72</v>
       </c>
       <c r="F3" s="2">
-        <v>215690</v>
+        <v>215642</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -22564,7 +22564,7 @@
         <v>144</v>
       </c>
       <c r="F20" s="2">
-        <v>14675</v>
+        <v>16675</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>10</v>
@@ -22699,7 +22699,7 @@
         <v>500</v>
       </c>
       <c r="F3" s="2">
-        <v>11065</v>
+        <v>10065</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>

--- a/frontend/public/reports/StockPulse_ESCOLAR.xlsx
+++ b/frontend/public/reports/StockPulse_ESCOLAR.xlsx
@@ -6695,7 +6695,7 @@
         <v>25</v>
       </c>
       <c r="F2" s="2">
-        <v>75638</v>
+        <v>73138</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -6718,7 +6718,7 @@
         <v>50</v>
       </c>
       <c r="F3" s="2">
-        <v>235977</v>
+        <v>230977</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -6787,7 +6787,7 @@
         <v>25</v>
       </c>
       <c r="F6" s="2">
-        <v>1627</v>
+        <v>1127</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>10</v>
@@ -6902,7 +6902,7 @@
         <v>36</v>
       </c>
       <c r="F11" s="2">
-        <v>29604</v>
+        <v>28524</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>10</v>
@@ -6925,7 +6925,7 @@
         <v>25</v>
       </c>
       <c r="F12" s="2">
-        <v>25453</v>
+        <v>24203</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>10</v>
@@ -6948,7 +6948,7 @@
         <v>50</v>
       </c>
       <c r="F13" s="2">
-        <v>128213</v>
+        <v>123213</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>10</v>
@@ -7313,7 +7313,7 @@
         <v>400</v>
       </c>
       <c r="F14" s="2">
-        <v>15802</v>
+        <v>11802</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>10</v>
@@ -12094,7 +12094,7 @@
         <v>64</v>
       </c>
       <c r="F190" s="2">
-        <v>10090</v>
+        <v>9770</v>
       </c>
       <c r="G190" s="3" t="s">
         <v>10</v>
@@ -14046,7 +14046,7 @@
         <v>72</v>
       </c>
       <c r="F8" s="2">
-        <v>15289</v>
+        <v>14569</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>10</v>
@@ -14253,7 +14253,7 @@
         <v>72</v>
       </c>
       <c r="F17" s="2">
-        <v>98101</v>
+        <v>95941</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>10</v>
@@ -14276,7 +14276,7 @@
         <v>72</v>
       </c>
       <c r="F18" s="2">
-        <v>8011</v>
+        <v>6571</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>10</v>
@@ -14414,7 +14414,7 @@
         <v>48</v>
       </c>
       <c r="F24" s="2">
-        <v>12202</v>
+        <v>10762</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>10</v>
@@ -15699,7 +15699,7 @@
         <v>144</v>
       </c>
       <c r="F2" s="2">
-        <v>74607</v>
+        <v>73167</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -15722,7 +15722,7 @@
         <v>144</v>
       </c>
       <c r="F3" s="2">
-        <v>37793</v>
+        <v>37073</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -16158,11 +16158,11 @@
       <c r="E22">
         <v>192</v>
       </c>
-      <c r="F22" s="2">
-        <v>1030</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>10</v>
+      <c r="F22" s="6">
+        <v>646</v>
+      </c>
+      <c r="G22" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -16181,11 +16181,11 @@
       <c r="E23">
         <v>192</v>
       </c>
-      <c r="F23" s="4">
-        <v>0</v>
-      </c>
-      <c r="G23" s="5" t="s">
-        <v>19</v>
+      <c r="F23" s="6">
+        <v>1</v>
+      </c>
+      <c r="G23" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -16205,7 +16205,7 @@
         <v>96</v>
       </c>
       <c r="F24" s="2">
-        <v>3510</v>
+        <v>3318</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>10</v>
@@ -16366,7 +16366,7 @@
         <v>96</v>
       </c>
       <c r="F31" s="2">
-        <v>11901</v>
+        <v>11709</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>10</v>
@@ -17861,7 +17861,7 @@
         <v>144</v>
       </c>
       <c r="F96" s="2">
-        <v>190794</v>
+        <v>190506</v>
       </c>
       <c r="G96" s="3" t="s">
         <v>10</v>
@@ -19192,7 +19192,7 @@
         <v>72</v>
       </c>
       <c r="F9" s="2">
-        <v>8629</v>
+        <v>8557</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>10</v>
@@ -19215,7 +19215,7 @@
         <v>120</v>
       </c>
       <c r="F10" s="2">
-        <v>11508</v>
+        <v>11268</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>10</v>
@@ -19698,7 +19698,7 @@
         <v>144</v>
       </c>
       <c r="F31" s="2">
-        <v>153771</v>
+        <v>139371</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>10</v>
@@ -19744,7 +19744,7 @@
         <v>120</v>
       </c>
       <c r="F33" s="2">
-        <v>39992</v>
+        <v>39392</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>10</v>
@@ -19790,7 +19790,7 @@
         <v>120</v>
       </c>
       <c r="F35" s="6">
-        <v>568</v>
+        <v>88</v>
       </c>
       <c r="G35" s="7" t="s">
         <v>49</v>
@@ -19813,7 +19813,7 @@
         <v>120</v>
       </c>
       <c r="F36" s="2">
-        <v>27575</v>
+        <v>26375</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>10</v>
@@ -19836,7 +19836,7 @@
         <v>120</v>
       </c>
       <c r="F37" s="2">
-        <v>10930</v>
+        <v>9730</v>
       </c>
       <c r="G37" s="3" t="s">
         <v>10</v>
@@ -19859,7 +19859,7 @@
         <v>120</v>
       </c>
       <c r="F38" s="2">
-        <v>101256</v>
+        <v>101016</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>10</v>
@@ -19882,7 +19882,7 @@
         <v>120</v>
       </c>
       <c r="F39" s="2">
-        <v>16346</v>
+        <v>16226</v>
       </c>
       <c r="G39" s="3" t="s">
         <v>10</v>
@@ -19905,7 +19905,7 @@
         <v>120</v>
       </c>
       <c r="F40" s="2">
-        <v>2448</v>
+        <v>2088</v>
       </c>
       <c r="G40" s="3" t="s">
         <v>10</v>
@@ -20273,7 +20273,7 @@
         <v>144</v>
       </c>
       <c r="F56" s="6">
-        <v>19</v>
+        <v>265</v>
       </c>
       <c r="G56" s="7" t="s">
         <v>49</v>
@@ -20848,7 +20848,7 @@
         <v>144</v>
       </c>
       <c r="F81" s="6">
-        <v>319</v>
+        <v>19</v>
       </c>
       <c r="G81" s="7" t="s">
         <v>49</v>
@@ -21282,7 +21282,7 @@
         <v>72</v>
       </c>
       <c r="F3" s="2">
-        <v>215642</v>
+        <v>212042</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -21486,7 +21486,7 @@
         <v>24</v>
       </c>
       <c r="F6" s="2">
-        <v>721</v>
+        <v>553</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>10</v>
@@ -21509,7 +21509,7 @@
         <v>24</v>
       </c>
       <c r="F7" s="2">
-        <v>433</v>
+        <v>313</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>10</v>
@@ -21670,7 +21670,7 @@
         <v>24</v>
       </c>
       <c r="F14" s="2">
-        <v>486</v>
+        <v>342</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>10</v>
@@ -21693,7 +21693,7 @@
         <v>24</v>
       </c>
       <c r="F15" s="2">
-        <v>692</v>
+        <v>548</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>10</v>
@@ -21762,7 +21762,7 @@
         <v>24</v>
       </c>
       <c r="F18" s="2">
-        <v>243</v>
+        <v>171</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>10</v>
@@ -21900,7 +21900,7 @@
         <v>24</v>
       </c>
       <c r="F24" s="2">
-        <v>616</v>
+        <v>472</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>10</v>
@@ -21923,7 +21923,7 @@
         <v>24</v>
       </c>
       <c r="F25" s="2">
-        <v>427</v>
+        <v>235</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>10</v>
@@ -22380,7 +22380,7 @@
         <v>192</v>
       </c>
       <c r="F12" s="2">
-        <v>37974</v>
+        <v>34134</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>10</v>
@@ -22403,7 +22403,7 @@
         <v>576</v>
       </c>
       <c r="F13" s="2">
-        <v>92896</v>
+        <v>91168</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>10</v>
@@ -22426,7 +22426,7 @@
         <v>12</v>
       </c>
       <c r="F14" s="2">
-        <v>91771</v>
+        <v>82171</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>10</v>
@@ -22449,7 +22449,7 @@
         <v>24</v>
       </c>
       <c r="F15" s="2">
-        <v>11105</v>
+        <v>1505</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>10</v>
@@ -22472,7 +22472,7 @@
         <v>48</v>
       </c>
       <c r="F16" s="2">
-        <v>15916</v>
+        <v>8716</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>10</v>
@@ -22837,7 +22837,7 @@
         <v>200</v>
       </c>
       <c r="F9" s="2">
-        <v>40773</v>
+        <v>34773</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>10</v>
@@ -22998,7 +22998,7 @@
         <v>200</v>
       </c>
       <c r="F16" s="2">
-        <v>2747</v>
+        <v>2347</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>10</v>

--- a/frontend/public/reports/StockPulse_ESCOLAR.xlsx
+++ b/frontend/public/reports/StockPulse_ESCOLAR.xlsx
@@ -6695,7 +6695,7 @@
         <v>25</v>
       </c>
       <c r="F2" s="2">
-        <v>73138</v>
+        <v>72138</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -6718,7 +6718,7 @@
         <v>50</v>
       </c>
       <c r="F3" s="2">
-        <v>230977</v>
+        <v>230477</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -6741,7 +6741,7 @@
         <v>100</v>
       </c>
       <c r="F4" s="2">
-        <v>82862</v>
+        <v>82312</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>10</v>
@@ -6787,7 +6787,7 @@
         <v>25</v>
       </c>
       <c r="F6" s="2">
-        <v>1127</v>
+        <v>752</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>10</v>
@@ -6856,7 +6856,7 @@
         <v>48</v>
       </c>
       <c r="F9" s="2">
-        <v>83857</v>
+        <v>83713</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>10</v>
@@ -6902,7 +6902,7 @@
         <v>36</v>
       </c>
       <c r="F11" s="2">
-        <v>28524</v>
+        <v>28416</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>10</v>
@@ -6925,7 +6925,7 @@
         <v>25</v>
       </c>
       <c r="F12" s="2">
-        <v>24203</v>
+        <v>23578</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>10</v>
@@ -7839,7 +7839,7 @@
         <v>50</v>
       </c>
       <c r="F5" s="2">
-        <v>11704</v>
+        <v>20254</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -7885,7 +7885,7 @@
         <v>50</v>
       </c>
       <c r="F7" s="2">
-        <v>7539</v>
+        <v>7239</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>10</v>
@@ -7931,7 +7931,7 @@
         <v>50</v>
       </c>
       <c r="F9" s="2">
-        <v>3643</v>
+        <v>3543</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>10</v>
@@ -8023,7 +8023,7 @@
         <v>50</v>
       </c>
       <c r="F13" s="2">
-        <v>4375</v>
+        <v>4325</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>10</v>
@@ -8115,7 +8115,7 @@
         <v>50</v>
       </c>
       <c r="F17" s="2">
-        <v>8132</v>
+        <v>8032</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>10</v>
@@ -8138,7 +8138,7 @@
         <v>50</v>
       </c>
       <c r="F18" s="2">
-        <v>15619</v>
+        <v>15519</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>10</v>
@@ -8598,7 +8598,7 @@
         <v>50</v>
       </c>
       <c r="F38" s="2">
-        <v>4321</v>
+        <v>4261</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>10</v>
@@ -9334,7 +9334,7 @@
         <v>100</v>
       </c>
       <c r="F70" s="2">
-        <v>5067</v>
+        <v>3567</v>
       </c>
       <c r="G70" s="3" t="s">
         <v>10</v>
@@ -11035,11 +11035,11 @@
       <c r="E144">
         <v>24</v>
       </c>
-      <c r="F144" s="4">
-        <v>0</v>
-      </c>
-      <c r="G144" s="5" t="s">
-        <v>19</v>
+      <c r="F144" s="6">
+        <v>17</v>
+      </c>
+      <c r="G144" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.25">
@@ -11174,7 +11174,7 @@
         <v>12</v>
       </c>
       <c r="F150" s="2">
-        <v>543</v>
+        <v>2559</v>
       </c>
       <c r="G150" s="3" t="s">
         <v>10</v>
@@ -11427,7 +11427,7 @@
         <v>24</v>
       </c>
       <c r="F161" s="2">
-        <v>922</v>
+        <v>898</v>
       </c>
       <c r="G161" s="3" t="s">
         <v>10</v>
@@ -11450,7 +11450,7 @@
         <v>24</v>
       </c>
       <c r="F162" s="2">
-        <v>1843</v>
+        <v>1747</v>
       </c>
       <c r="G162" s="3" t="s">
         <v>10</v>
@@ -11473,7 +11473,7 @@
         <v>24</v>
       </c>
       <c r="F163" s="2">
-        <v>586</v>
+        <v>562</v>
       </c>
       <c r="G163" s="3" t="s">
         <v>10</v>
@@ -11496,7 +11496,7 @@
         <v>24</v>
       </c>
       <c r="F164" s="2">
-        <v>996</v>
+        <v>948</v>
       </c>
       <c r="G164" s="3" t="s">
         <v>10</v>
@@ -14023,7 +14023,7 @@
         <v>144</v>
       </c>
       <c r="F7" s="2">
-        <v>104051</v>
+        <v>104049</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>10</v>
@@ -14046,7 +14046,7 @@
         <v>72</v>
       </c>
       <c r="F8" s="2">
-        <v>14569</v>
+        <v>14567</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>10</v>
@@ -14460,7 +14460,7 @@
         <v>60</v>
       </c>
       <c r="F26" s="2">
-        <v>32615</v>
+        <v>32613</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>10</v>
@@ -14483,7 +14483,7 @@
         <v>60</v>
       </c>
       <c r="F27" s="2">
-        <v>71458</v>
+        <v>71446</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>10</v>
@@ -15699,7 +15699,7 @@
         <v>144</v>
       </c>
       <c r="F2" s="2">
-        <v>73167</v>
+        <v>73166</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -17148,7 +17148,7 @@
         <v>200</v>
       </c>
       <c r="F65" s="2">
-        <v>4930</v>
+        <v>4906</v>
       </c>
       <c r="G65" s="3" t="s">
         <v>10</v>
@@ -17171,7 +17171,7 @@
         <v>200</v>
       </c>
       <c r="F66" s="2">
-        <v>7447</v>
+        <v>7347</v>
       </c>
       <c r="G66" s="3" t="s">
         <v>10</v>
@@ -17631,7 +17631,7 @@
         <v>576</v>
       </c>
       <c r="F86" s="2">
-        <v>19918</v>
+        <v>19868</v>
       </c>
       <c r="G86" s="3" t="s">
         <v>10</v>
@@ -17769,7 +17769,7 @@
         <v>576</v>
       </c>
       <c r="F92" s="2">
-        <v>4243</v>
+        <v>4231</v>
       </c>
       <c r="G92" s="3" t="s">
         <v>10</v>
@@ -17792,7 +17792,7 @@
         <v>576</v>
       </c>
       <c r="F93" s="2">
-        <v>14255</v>
+        <v>14231</v>
       </c>
       <c r="G93" s="3" t="s">
         <v>10</v>
@@ -17861,7 +17861,7 @@
         <v>144</v>
       </c>
       <c r="F96" s="2">
-        <v>190506</v>
+        <v>190504</v>
       </c>
       <c r="G96" s="3" t="s">
         <v>10</v>
@@ -17884,7 +17884,7 @@
         <v>288</v>
       </c>
       <c r="F97" s="2">
-        <v>25660</v>
+        <v>25656</v>
       </c>
       <c r="G97" s="3" t="s">
         <v>10</v>
@@ -19698,7 +19698,7 @@
         <v>144</v>
       </c>
       <c r="F31" s="2">
-        <v>139371</v>
+        <v>139363</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>10</v>
@@ -20848,7 +20848,7 @@
         <v>144</v>
       </c>
       <c r="F81" s="6">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G81" s="7" t="s">
         <v>49</v>
@@ -21417,7 +21417,7 @@
         <v>12</v>
       </c>
       <c r="F3" s="2">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -21440,7 +21440,7 @@
         <v>12</v>
       </c>
       <c r="F4" s="2">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>10</v>
@@ -21486,7 +21486,7 @@
         <v>24</v>
       </c>
       <c r="F6" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>10</v>
@@ -22219,7 +22219,7 @@
         <v>288</v>
       </c>
       <c r="F5" s="2">
-        <v>65701</v>
+        <v>65501</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -22426,7 +22426,7 @@
         <v>12</v>
       </c>
       <c r="F14" s="2">
-        <v>82171</v>
+        <v>82069</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>10</v>
@@ -22699,7 +22699,7 @@
         <v>500</v>
       </c>
       <c r="F3" s="2">
-        <v>10065</v>
+        <v>9965</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -22837,7 +22837,7 @@
         <v>200</v>
       </c>
       <c r="F9" s="2">
-        <v>34773</v>
+        <v>34772</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>10</v>

--- a/frontend/public/reports/StockPulse_ESCOLAR.xlsx
+++ b/frontend/public/reports/StockPulse_ESCOLAR.xlsx
@@ -6695,7 +6695,7 @@
         <v>25</v>
       </c>
       <c r="F2" s="2">
-        <v>72138</v>
+        <v>71888</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -6718,7 +6718,7 @@
         <v>50</v>
       </c>
       <c r="F3" s="2">
-        <v>230477</v>
+        <v>229877</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -6810,7 +6810,7 @@
         <v>25</v>
       </c>
       <c r="F7" s="2">
-        <v>9975</v>
+        <v>7425</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>10</v>
@@ -6902,7 +6902,7 @@
         <v>36</v>
       </c>
       <c r="F11" s="2">
-        <v>28416</v>
+        <v>28293</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>10</v>
@@ -6925,7 +6925,7 @@
         <v>25</v>
       </c>
       <c r="F12" s="2">
-        <v>23578</v>
+        <v>23453</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>10</v>
@@ -6948,7 +6948,7 @@
         <v>50</v>
       </c>
       <c r="F13" s="2">
-        <v>123213</v>
+        <v>123127</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>10</v>
@@ -7336,7 +7336,7 @@
         <v>100</v>
       </c>
       <c r="F15" s="2">
-        <v>39569</v>
+        <v>39469</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>10</v>
@@ -7474,7 +7474,7 @@
         <v>500</v>
       </c>
       <c r="F21" s="2">
-        <v>47755</v>
+        <v>47255</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>10</v>
@@ -7497,7 +7497,7 @@
         <v>500</v>
       </c>
       <c r="F22" s="2">
-        <v>24084</v>
+        <v>23584</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>10</v>
@@ -7885,7 +7885,7 @@
         <v>50</v>
       </c>
       <c r="F7" s="2">
-        <v>7239</v>
+        <v>7139</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>10</v>
@@ -7931,7 +7931,7 @@
         <v>50</v>
       </c>
       <c r="F9" s="2">
-        <v>3543</v>
+        <v>3493</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>10</v>
@@ -7954,7 +7954,7 @@
         <v>50</v>
       </c>
       <c r="F10" s="2">
-        <v>13854</v>
+        <v>13754</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>10</v>
@@ -7977,7 +7977,7 @@
         <v>50</v>
       </c>
       <c r="F11" s="2">
-        <v>5010</v>
+        <v>4960</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>10</v>
@@ -8068,11 +8068,11 @@
       <c r="E15">
         <v>50</v>
       </c>
-      <c r="F15" s="2">
-        <v>295</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>10</v>
+      <c r="F15" s="4">
+        <v>0</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -8092,7 +8092,7 @@
         <v>50</v>
       </c>
       <c r="F16" s="2">
-        <v>5017</v>
+        <v>4892</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>10</v>
@@ -8161,7 +8161,7 @@
         <v>50</v>
       </c>
       <c r="F19" s="2">
-        <v>2247</v>
+        <v>2197</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>10</v>
@@ -8207,7 +8207,7 @@
         <v>50</v>
       </c>
       <c r="F21" s="2">
-        <v>650</v>
+        <v>550</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>10</v>
@@ -8230,7 +8230,7 @@
         <v>50</v>
       </c>
       <c r="F22" s="2">
-        <v>643</v>
+        <v>593</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>10</v>
@@ -8414,7 +8414,7 @@
         <v>50</v>
       </c>
       <c r="F30" s="2">
-        <v>9626</v>
+        <v>9625</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>10</v>
@@ -8621,7 +8621,7 @@
         <v>50</v>
       </c>
       <c r="F39" s="2">
-        <v>2723</v>
+        <v>2722</v>
       </c>
       <c r="G39" s="3" t="s">
         <v>10</v>
@@ -8644,7 +8644,7 @@
         <v>50</v>
       </c>
       <c r="F40" s="2">
-        <v>7031</v>
+        <v>6981</v>
       </c>
       <c r="G40" s="3" t="s">
         <v>10</v>
@@ -8736,7 +8736,7 @@
         <v>100</v>
       </c>
       <c r="F44" s="2">
-        <v>3139</v>
+        <v>3339</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>10</v>
@@ -8782,7 +8782,7 @@
         <v>100</v>
       </c>
       <c r="F46" s="2">
-        <v>4764</v>
+        <v>4664</v>
       </c>
       <c r="G46" s="3" t="s">
         <v>10</v>
@@ -8805,7 +8805,7 @@
         <v>100</v>
       </c>
       <c r="F47" s="2">
-        <v>2713</v>
+        <v>2913</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>10</v>
@@ -8851,7 +8851,7 @@
         <v>100</v>
       </c>
       <c r="F49" s="2">
-        <v>1189</v>
+        <v>1389</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>10</v>
@@ -8897,7 +8897,7 @@
         <v>100</v>
       </c>
       <c r="F51" s="2">
-        <v>1192</v>
+        <v>1492</v>
       </c>
       <c r="G51" s="3" t="s">
         <v>10</v>
@@ -8920,7 +8920,7 @@
         <v>100</v>
       </c>
       <c r="F52" s="2">
-        <v>817</v>
+        <v>1017</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>10</v>
@@ -9334,7 +9334,7 @@
         <v>100</v>
       </c>
       <c r="F70" s="2">
-        <v>3567</v>
+        <v>1967</v>
       </c>
       <c r="G70" s="3" t="s">
         <v>10</v>
@@ -11312,7 +11312,7 @@
         <v>6</v>
       </c>
       <c r="F156" s="2">
-        <v>936</v>
+        <v>900</v>
       </c>
       <c r="G156" s="3" t="s">
         <v>10</v>
@@ -11565,7 +11565,7 @@
         <v>72</v>
       </c>
       <c r="F167" s="2">
-        <v>22562</v>
+        <v>22490</v>
       </c>
       <c r="G167" s="3" t="s">
         <v>10</v>
@@ -11588,7 +11588,7 @@
         <v>72</v>
       </c>
       <c r="F168" s="2">
-        <v>4260</v>
+        <v>4188</v>
       </c>
       <c r="G168" s="3" t="s">
         <v>10</v>
@@ -11611,7 +11611,7 @@
         <v>36</v>
       </c>
       <c r="F169" s="2">
-        <v>1404</v>
+        <v>1332</v>
       </c>
       <c r="G169" s="3" t="s">
         <v>10</v>
@@ -13977,7 +13977,7 @@
         <v>24</v>
       </c>
       <c r="F5" s="2">
-        <v>2283</v>
+        <v>2259</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -14023,7 +14023,7 @@
         <v>144</v>
       </c>
       <c r="F7" s="2">
-        <v>104049</v>
+        <v>103185</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>10</v>
@@ -14046,7 +14046,7 @@
         <v>72</v>
       </c>
       <c r="F8" s="2">
-        <v>14567</v>
+        <v>14495</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>10</v>
@@ -15699,7 +15699,7 @@
         <v>144</v>
       </c>
       <c r="F2" s="2">
-        <v>73166</v>
+        <v>73106</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -16090,7 +16090,7 @@
         <v>192</v>
       </c>
       <c r="F19" s="2">
-        <v>9494</v>
+        <v>9488</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>10</v>
@@ -16113,7 +16113,7 @@
         <v>192</v>
       </c>
       <c r="F20" s="2">
-        <v>14861</v>
+        <v>14855</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>10</v>
@@ -16228,7 +16228,7 @@
         <v>48</v>
       </c>
       <c r="F25" s="2">
-        <v>3794</v>
+        <v>3746</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>10</v>
@@ -16849,7 +16849,7 @@
         <v>144</v>
       </c>
       <c r="F52" s="2">
-        <v>7067</v>
+        <v>6779</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>10</v>
@@ -19698,7 +19698,7 @@
         <v>144</v>
       </c>
       <c r="F31" s="2">
-        <v>139363</v>
+        <v>138643</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>10</v>
@@ -19767,7 +19767,7 @@
         <v>120</v>
       </c>
       <c r="F34" s="2">
-        <v>48824</v>
+        <v>48704</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>10</v>
@@ -19813,7 +19813,7 @@
         <v>120</v>
       </c>
       <c r="F36" s="2">
-        <v>26375</v>
+        <v>26255</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>10</v>
@@ -19836,7 +19836,7 @@
         <v>120</v>
       </c>
       <c r="F37" s="2">
-        <v>9730</v>
+        <v>9490</v>
       </c>
       <c r="G37" s="3" t="s">
         <v>10</v>
@@ -20043,7 +20043,7 @@
         <v>144</v>
       </c>
       <c r="F46" s="2">
-        <v>8923</v>
+        <v>8851</v>
       </c>
       <c r="G46" s="3" t="s">
         <v>10</v>
@@ -20342,7 +20342,7 @@
         <v>144</v>
       </c>
       <c r="F59" s="2">
-        <v>4550</v>
+        <v>4514</v>
       </c>
       <c r="G59" s="3" t="s">
         <v>10</v>
@@ -20365,7 +20365,7 @@
         <v>144</v>
       </c>
       <c r="F60" s="2">
-        <v>3902</v>
+        <v>3866</v>
       </c>
       <c r="G60" s="3" t="s">
         <v>10</v>
@@ -20871,7 +20871,7 @@
         <v>144</v>
       </c>
       <c r="F82" s="2">
-        <v>1764</v>
+        <v>1656</v>
       </c>
       <c r="G82" s="3" t="s">
         <v>10</v>
@@ -21032,7 +21032,7 @@
         <v>144</v>
       </c>
       <c r="F89" s="2">
-        <v>6626</v>
+        <v>6578</v>
       </c>
       <c r="G89" s="3" t="s">
         <v>10</v>
@@ -21055,7 +21055,7 @@
         <v>144</v>
       </c>
       <c r="F90" s="2">
-        <v>18282</v>
+        <v>18222</v>
       </c>
       <c r="G90" s="3" t="s">
         <v>10</v>
@@ -21328,7 +21328,7 @@
         <v>72</v>
       </c>
       <c r="F5" s="2">
-        <v>32978</v>
+        <v>32954</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -22768,7 +22768,7 @@
         <v>500</v>
       </c>
       <c r="F6" s="6">
-        <v>207</v>
+        <v>157</v>
       </c>
       <c r="G6" s="7" t="s">
         <v>49</v>

--- a/frontend/public/reports/StockPulse_ESCOLAR.xlsx
+++ b/frontend/public/reports/StockPulse_ESCOLAR.xlsx
@@ -6787,7 +6787,7 @@
         <v>25</v>
       </c>
       <c r="F6" s="2">
-        <v>752</v>
+        <v>502</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>10</v>
@@ -6902,7 +6902,7 @@
         <v>36</v>
       </c>
       <c r="F11" s="2">
-        <v>28293</v>
+        <v>27933</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>10</v>
@@ -6948,7 +6948,7 @@
         <v>50</v>
       </c>
       <c r="F13" s="2">
-        <v>123127</v>
+        <v>122627</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>10</v>
@@ -7793,7 +7793,7 @@
         <v>50</v>
       </c>
       <c r="F3" s="2">
-        <v>46970</v>
+        <v>46720</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -7839,7 +7839,7 @@
         <v>50</v>
       </c>
       <c r="F5" s="2">
-        <v>20254</v>
+        <v>18254</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -10461,7 +10461,7 @@
         <v>24</v>
       </c>
       <c r="F119" s="2">
-        <v>25116</v>
+        <v>22716</v>
       </c>
       <c r="G119" s="3" t="s">
         <v>10</v>
@@ -14253,7 +14253,7 @@
         <v>72</v>
       </c>
       <c r="F17" s="2">
-        <v>95941</v>
+        <v>95653</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>10</v>
@@ -14276,7 +14276,7 @@
         <v>72</v>
       </c>
       <c r="F18" s="2">
-        <v>6571</v>
+        <v>6427</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>10</v>
@@ -14391,7 +14391,7 @@
         <v>60</v>
       </c>
       <c r="F23" s="2">
-        <v>13508</v>
+        <v>13268</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>10</v>
@@ -15768,7 +15768,7 @@
         <v>288</v>
       </c>
       <c r="F5" s="6">
-        <v>1038</v>
+        <v>750</v>
       </c>
       <c r="G5" s="7" t="s">
         <v>49</v>
@@ -16251,7 +16251,7 @@
         <v>24</v>
       </c>
       <c r="F26" s="2">
-        <v>13300</v>
+        <v>12943</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>10</v>
@@ -16872,7 +16872,7 @@
         <v>96</v>
       </c>
       <c r="F53" s="2">
-        <v>14685</v>
+        <v>14589</v>
       </c>
       <c r="G53" s="3" t="s">
         <v>10</v>
@@ -19353,7 +19353,7 @@
         <v>24</v>
       </c>
       <c r="F16" s="6">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G16" s="7" t="s">
         <v>49</v>
@@ -19375,11 +19375,11 @@
       <c r="E17">
         <v>24</v>
       </c>
-      <c r="F17" s="4">
-        <v>0</v>
-      </c>
-      <c r="G17" s="5" t="s">
-        <v>19</v>
+      <c r="F17" s="6">
+        <v>1</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -19398,11 +19398,11 @@
       <c r="E18">
         <v>24</v>
       </c>
-      <c r="F18" s="4">
-        <v>0</v>
-      </c>
-      <c r="G18" s="5" t="s">
-        <v>19</v>
+      <c r="F18" s="6">
+        <v>1</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -19928,7 +19928,7 @@
         <v>144</v>
       </c>
       <c r="F41" s="2">
-        <v>7394</v>
+        <v>7250</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>10</v>

--- a/frontend/public/reports/StockPulse_ESCOLAR.xlsx
+++ b/frontend/public/reports/StockPulse_ESCOLAR.xlsx
@@ -6741,7 +6741,7 @@
         <v>100</v>
       </c>
       <c r="F4" s="2">
-        <v>82312</v>
+        <v>80312</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>10</v>
@@ -6810,7 +6810,7 @@
         <v>25</v>
       </c>
       <c r="F7" s="2">
-        <v>7425</v>
+        <v>6425</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>10</v>
@@ -6833,7 +6833,7 @@
         <v>48</v>
       </c>
       <c r="F8" s="2">
-        <v>69708</v>
+        <v>68748</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>10</v>
@@ -6902,7 +6902,7 @@
         <v>36</v>
       </c>
       <c r="F11" s="2">
-        <v>27933</v>
+        <v>27213</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>10</v>
@@ -6925,7 +6925,7 @@
         <v>25</v>
       </c>
       <c r="F12" s="2">
-        <v>23453</v>
+        <v>18203</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>10</v>
@@ -6948,7 +6948,7 @@
         <v>50</v>
       </c>
       <c r="F13" s="2">
-        <v>122627</v>
+        <v>117627</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>10</v>
@@ -7175,7 +7175,7 @@
         <v>48</v>
       </c>
       <c r="F8" s="2">
-        <v>10052</v>
+        <v>9956</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>10</v>
@@ -7198,7 +7198,7 @@
         <v>48</v>
       </c>
       <c r="F9" s="2">
-        <v>2036</v>
+        <v>1940</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>10</v>
@@ -7336,7 +7336,7 @@
         <v>100</v>
       </c>
       <c r="F15" s="2">
-        <v>39469</v>
+        <v>38969</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>10</v>
@@ -7359,7 +7359,7 @@
         <v>72</v>
       </c>
       <c r="F16" s="2">
-        <v>2310</v>
+        <v>2094</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>10</v>
@@ -7382,7 +7382,7 @@
         <v>72</v>
       </c>
       <c r="F17" s="2">
-        <v>14034</v>
+        <v>13746</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>10</v>
@@ -7404,11 +7404,11 @@
       <c r="E18">
         <v>288</v>
       </c>
-      <c r="F18" s="6">
-        <v>542</v>
-      </c>
-      <c r="G18" s="7" t="s">
-        <v>49</v>
+      <c r="F18" s="4">
+        <v>0</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -7474,7 +7474,7 @@
         <v>500</v>
       </c>
       <c r="F21" s="2">
-        <v>47255</v>
+        <v>45255</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>10</v>
@@ -7497,7 +7497,7 @@
         <v>500</v>
       </c>
       <c r="F22" s="2">
-        <v>23584</v>
+        <v>22084</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>10</v>
@@ -7519,11 +7519,11 @@
       <c r="E23">
         <v>300</v>
       </c>
-      <c r="F23" s="2">
-        <v>1775</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>10</v>
+      <c r="F23" s="6">
+        <v>1175</v>
+      </c>
+      <c r="G23" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -7589,7 +7589,7 @@
         <v>120</v>
       </c>
       <c r="F26" s="2">
-        <v>3104</v>
+        <v>2864</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>10</v>
@@ -7704,7 +7704,7 @@
         <v>100</v>
       </c>
       <c r="F31" s="2">
-        <v>1351</v>
+        <v>1251</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>10</v>
@@ -7839,7 +7839,7 @@
         <v>50</v>
       </c>
       <c r="F5" s="2">
-        <v>18254</v>
+        <v>15754</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -7885,7 +7885,7 @@
         <v>50</v>
       </c>
       <c r="F7" s="2">
-        <v>7139</v>
+        <v>6939</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>10</v>
@@ -7954,7 +7954,7 @@
         <v>50</v>
       </c>
       <c r="F10" s="2">
-        <v>13754</v>
+        <v>13654</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>10</v>
@@ -8000,7 +8000,7 @@
         <v>50</v>
       </c>
       <c r="F12" s="2">
-        <v>3009</v>
+        <v>2859</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>10</v>
@@ -8046,7 +8046,7 @@
         <v>50</v>
       </c>
       <c r="F14" s="6">
-        <v>171</v>
+        <v>21</v>
       </c>
       <c r="G14" s="7" t="s">
         <v>49</v>
@@ -8115,7 +8115,7 @@
         <v>50</v>
       </c>
       <c r="F17" s="2">
-        <v>8032</v>
+        <v>7882</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>10</v>
@@ -8138,7 +8138,7 @@
         <v>50</v>
       </c>
       <c r="F18" s="2">
-        <v>15519</v>
+        <v>15119</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>10</v>
@@ -8161,7 +8161,7 @@
         <v>50</v>
       </c>
       <c r="F19" s="2">
-        <v>2197</v>
+        <v>1897</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>10</v>
@@ -8206,11 +8206,11 @@
       <c r="E21">
         <v>50</v>
       </c>
-      <c r="F21" s="2">
-        <v>550</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>10</v>
+      <c r="F21" s="6">
+        <v>100</v>
+      </c>
+      <c r="G21" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -8230,7 +8230,7 @@
         <v>50</v>
       </c>
       <c r="F22" s="2">
-        <v>593</v>
+        <v>493</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>10</v>
@@ -8736,7 +8736,7 @@
         <v>100</v>
       </c>
       <c r="F44" s="2">
-        <v>3339</v>
+        <v>3289</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>10</v>
@@ -8759,7 +8759,7 @@
         <v>100</v>
       </c>
       <c r="F45" s="2">
-        <v>2776</v>
+        <v>2726</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>10</v>
@@ -8805,7 +8805,7 @@
         <v>100</v>
       </c>
       <c r="F47" s="2">
-        <v>2913</v>
+        <v>2813</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>10</v>
@@ -8851,7 +8851,7 @@
         <v>100</v>
       </c>
       <c r="F49" s="2">
-        <v>1389</v>
+        <v>1339</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>10</v>
@@ -8874,7 +8874,7 @@
         <v>100</v>
       </c>
       <c r="F50" s="2">
-        <v>2223</v>
+        <v>2173</v>
       </c>
       <c r="G50" s="3" t="s">
         <v>10</v>
@@ -8920,7 +8920,7 @@
         <v>100</v>
       </c>
       <c r="F52" s="2">
-        <v>1017</v>
+        <v>917</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>10</v>
@@ -9495,7 +9495,7 @@
         <v>100</v>
       </c>
       <c r="F77" s="2">
-        <v>43324</v>
+        <v>42324</v>
       </c>
       <c r="G77" s="3" t="s">
         <v>10</v>
@@ -9564,7 +9564,7 @@
         <v>100</v>
       </c>
       <c r="F80" s="2">
-        <v>16423</v>
+        <v>15923</v>
       </c>
       <c r="G80" s="3" t="s">
         <v>10</v>
@@ -9587,7 +9587,7 @@
         <v>100</v>
       </c>
       <c r="F81" s="2">
-        <v>10217</v>
+        <v>9717</v>
       </c>
       <c r="G81" s="3" t="s">
         <v>10</v>
@@ -9656,7 +9656,7 @@
         <v>100</v>
       </c>
       <c r="F84" s="2">
-        <v>3092</v>
+        <v>2592</v>
       </c>
       <c r="G84" s="3" t="s">
         <v>10</v>
@@ -9955,7 +9955,7 @@
         <v>120</v>
       </c>
       <c r="F97" s="2">
-        <v>2487</v>
+        <v>2247</v>
       </c>
       <c r="G97" s="3" t="s">
         <v>10</v>
@@ -10024,7 +10024,7 @@
         <v>120</v>
       </c>
       <c r="F100" s="2">
-        <v>1340</v>
+        <v>1100</v>
       </c>
       <c r="G100" s="3" t="s">
         <v>10</v>
@@ -10530,7 +10530,7 @@
         <v>24</v>
       </c>
       <c r="F122" s="2">
-        <v>3713</v>
+        <v>3593</v>
       </c>
       <c r="G122" s="3" t="s">
         <v>10</v>
@@ -10599,7 +10599,7 @@
         <v>24</v>
       </c>
       <c r="F125" s="2">
-        <v>595</v>
+        <v>475</v>
       </c>
       <c r="G125" s="3" t="s">
         <v>10</v>
@@ -10737,7 +10737,7 @@
         <v>24</v>
       </c>
       <c r="F131" s="2">
-        <v>9834</v>
+        <v>9762</v>
       </c>
       <c r="G131" s="3" t="s">
         <v>10</v>
@@ -11380,11 +11380,11 @@
       <c r="E159">
         <v>24</v>
       </c>
-      <c r="F159" s="2">
-        <v>130</v>
-      </c>
-      <c r="G159" s="3" t="s">
-        <v>10</v>
+      <c r="F159" s="6">
+        <v>34</v>
+      </c>
+      <c r="G159" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.25">
@@ -11427,7 +11427,7 @@
         <v>24</v>
       </c>
       <c r="F161" s="2">
-        <v>898</v>
+        <v>778</v>
       </c>
       <c r="G161" s="3" t="s">
         <v>10</v>
@@ -11473,7 +11473,7 @@
         <v>24</v>
       </c>
       <c r="F163" s="2">
-        <v>562</v>
+        <v>490</v>
       </c>
       <c r="G163" s="3" t="s">
         <v>10</v>
@@ -11519,7 +11519,7 @@
         <v>24</v>
       </c>
       <c r="F165" s="2">
-        <v>1246</v>
+        <v>1126</v>
       </c>
       <c r="G165" s="3" t="s">
         <v>10</v>
@@ -11703,7 +11703,7 @@
         <v>72</v>
       </c>
       <c r="F173" s="2">
-        <v>1193</v>
+        <v>1121</v>
       </c>
       <c r="G173" s="3" t="s">
         <v>10</v>
@@ -11795,7 +11795,7 @@
         <v>48</v>
       </c>
       <c r="F177" s="6">
-        <v>193</v>
+        <v>97</v>
       </c>
       <c r="G177" s="7" t="s">
         <v>49</v>
@@ -11818,7 +11818,7 @@
         <v>48</v>
       </c>
       <c r="F178" s="2">
-        <v>520</v>
+        <v>424</v>
       </c>
       <c r="G178" s="3" t="s">
         <v>10</v>
@@ -11840,11 +11840,11 @@
       <c r="E179">
         <v>36</v>
       </c>
-      <c r="F179" s="2">
-        <v>218</v>
-      </c>
-      <c r="G179" s="3" t="s">
-        <v>10</v>
+      <c r="F179" s="6">
+        <v>146</v>
+      </c>
+      <c r="G179" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.25">
@@ -11910,7 +11910,7 @@
         <v>36</v>
       </c>
       <c r="F182" s="2">
-        <v>922</v>
+        <v>850</v>
       </c>
       <c r="G182" s="3" t="s">
         <v>10</v>
@@ -12094,7 +12094,7 @@
         <v>64</v>
       </c>
       <c r="F190" s="2">
-        <v>9770</v>
+        <v>9450</v>
       </c>
       <c r="G190" s="3" t="s">
         <v>10</v>
@@ -13267,7 +13267,7 @@
         <v>5</v>
       </c>
       <c r="F241" s="2">
-        <v>1705</v>
+        <v>1695</v>
       </c>
       <c r="G241" s="3" t="s">
         <v>10</v>
@@ -13313,7 +13313,7 @@
         <v>5</v>
       </c>
       <c r="F243" s="2">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="G243" s="3" t="s">
         <v>10</v>
@@ -13405,7 +13405,7 @@
         <v>5</v>
       </c>
       <c r="F247" s="2">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="G247" s="3" t="s">
         <v>10</v>
@@ -13497,7 +13497,7 @@
         <v>40</v>
       </c>
       <c r="F251" s="2">
-        <v>4427</v>
+        <v>3227</v>
       </c>
       <c r="G251" s="3" t="s">
         <v>10</v>
@@ -13566,7 +13566,7 @@
         <v>40</v>
       </c>
       <c r="F254" s="2">
-        <v>141054</v>
+        <v>135054</v>
       </c>
       <c r="G254" s="3" t="s">
         <v>10</v>
@@ -13908,7 +13908,7 @@
         <v>288</v>
       </c>
       <c r="F2" s="2">
-        <v>25237</v>
+        <v>24949</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -14138,7 +14138,7 @@
         <v>144</v>
       </c>
       <c r="F12" s="2">
-        <v>15523</v>
+        <v>14383</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>10</v>
@@ -14184,7 +14184,7 @@
         <v>144</v>
       </c>
       <c r="F14" s="2">
-        <v>10060</v>
+        <v>9628</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>10</v>
@@ -14299,7 +14299,7 @@
         <v>36</v>
       </c>
       <c r="F19" s="2">
-        <v>5063</v>
+        <v>4991</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>10</v>
@@ -14391,7 +14391,7 @@
         <v>60</v>
       </c>
       <c r="F23" s="2">
-        <v>13268</v>
+        <v>12968</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>10</v>
@@ -14414,7 +14414,7 @@
         <v>48</v>
       </c>
       <c r="F24" s="2">
-        <v>10762</v>
+        <v>9802</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>10</v>
@@ -14460,7 +14460,7 @@
         <v>60</v>
       </c>
       <c r="F26" s="2">
-        <v>32613</v>
+        <v>32313</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>10</v>
@@ -14483,7 +14483,7 @@
         <v>60</v>
       </c>
       <c r="F27" s="2">
-        <v>71446</v>
+        <v>71146</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>10</v>
@@ -14966,7 +14966,7 @@
         <v>144</v>
       </c>
       <c r="F48" s="2">
-        <v>49096</v>
+        <v>46936</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>10</v>
@@ -15035,7 +15035,7 @@
         <v>360</v>
       </c>
       <c r="F51" s="2">
-        <v>27538</v>
+        <v>23938</v>
       </c>
       <c r="G51" s="3" t="s">
         <v>10</v>
@@ -15883,7 +15883,7 @@
         <v>288</v>
       </c>
       <c r="F10" s="2">
-        <v>9360</v>
+        <v>9072</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>10</v>
@@ -15975,7 +15975,7 @@
         <v>96</v>
       </c>
       <c r="F14" s="2">
-        <v>9345</v>
+        <v>9249</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>10</v>
@@ -15998,7 +15998,7 @@
         <v>96</v>
       </c>
       <c r="F15" s="2">
-        <v>7647</v>
+        <v>7551</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>10</v>
@@ -16159,7 +16159,7 @@
         <v>192</v>
       </c>
       <c r="F22" s="6">
-        <v>646</v>
+        <v>454</v>
       </c>
       <c r="G22" s="7" t="s">
         <v>49</v>
@@ -16205,7 +16205,7 @@
         <v>96</v>
       </c>
       <c r="F24" s="2">
-        <v>3318</v>
+        <v>3222</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>10</v>
@@ -16803,7 +16803,7 @@
         <v>144</v>
       </c>
       <c r="F50" s="2">
-        <v>15140</v>
+        <v>14996</v>
       </c>
       <c r="G50" s="3" t="s">
         <v>10</v>
@@ -16872,7 +16872,7 @@
         <v>96</v>
       </c>
       <c r="F53" s="2">
-        <v>14589</v>
+        <v>14109</v>
       </c>
       <c r="G53" s="3" t="s">
         <v>10</v>
@@ -17263,7 +17263,7 @@
         <v>200</v>
       </c>
       <c r="F70" s="2">
-        <v>9581</v>
+        <v>8581</v>
       </c>
       <c r="G70" s="3" t="s">
         <v>10</v>
@@ -17401,7 +17401,7 @@
         <v>200</v>
       </c>
       <c r="F76" s="2">
-        <v>60988</v>
+        <v>57988</v>
       </c>
       <c r="G76" s="3" t="s">
         <v>10</v>
@@ -17539,7 +17539,7 @@
         <v>1152</v>
       </c>
       <c r="F82" s="2">
-        <v>61922</v>
+        <v>56162</v>
       </c>
       <c r="G82" s="3" t="s">
         <v>10</v>
@@ -17654,7 +17654,7 @@
         <v>576</v>
       </c>
       <c r="F87" s="2">
-        <v>4143</v>
+        <v>2991</v>
       </c>
       <c r="G87" s="3" t="s">
         <v>10</v>
@@ -19077,7 +19077,7 @@
         <v>50</v>
       </c>
       <c r="F4" s="2">
-        <v>11431</v>
+        <v>11181</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>10</v>
@@ -19583,7 +19583,7 @@
         <v>36</v>
       </c>
       <c r="F26" s="2">
-        <v>5385</v>
+        <v>5313</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>10</v>
@@ -19629,7 +19629,7 @@
         <v>36</v>
       </c>
       <c r="F28" s="2">
-        <v>3655</v>
+        <v>3583</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>10</v>
@@ -19652,7 +19652,7 @@
         <v>36</v>
       </c>
       <c r="F29" s="2">
-        <v>5310</v>
+        <v>5166</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>10</v>
@@ -19744,7 +19744,7 @@
         <v>120</v>
       </c>
       <c r="F33" s="2">
-        <v>39392</v>
+        <v>38192</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>10</v>
@@ -19767,7 +19767,7 @@
         <v>120</v>
       </c>
       <c r="F34" s="2">
-        <v>48704</v>
+        <v>47264</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>10</v>
@@ -19789,11 +19789,11 @@
       <c r="E35">
         <v>120</v>
       </c>
-      <c r="F35" s="6">
-        <v>88</v>
-      </c>
-      <c r="G35" s="7" t="s">
-        <v>49</v>
+      <c r="F35" s="4">
+        <v>0</v>
+      </c>
+      <c r="G35" s="5" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
@@ -19836,7 +19836,7 @@
         <v>120</v>
       </c>
       <c r="F37" s="2">
-        <v>9490</v>
+        <v>7090</v>
       </c>
       <c r="G37" s="3" t="s">
         <v>10</v>
@@ -19859,7 +19859,7 @@
         <v>120</v>
       </c>
       <c r="F38" s="2">
-        <v>101016</v>
+        <v>100416</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>10</v>
@@ -19882,7 +19882,7 @@
         <v>120</v>
       </c>
       <c r="F39" s="2">
-        <v>16226</v>
+        <v>15746</v>
       </c>
       <c r="G39" s="3" t="s">
         <v>10</v>
@@ -19905,7 +19905,7 @@
         <v>120</v>
       </c>
       <c r="F40" s="2">
-        <v>2088</v>
+        <v>888</v>
       </c>
       <c r="G40" s="3" t="s">
         <v>10</v>
@@ -19928,7 +19928,7 @@
         <v>144</v>
       </c>
       <c r="F41" s="2">
-        <v>7250</v>
+        <v>6242</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>10</v>
@@ -19951,7 +19951,7 @@
         <v>144</v>
       </c>
       <c r="F42" s="2">
-        <v>11077</v>
+        <v>10645</v>
       </c>
       <c r="G42" s="3" t="s">
         <v>10</v>
@@ -19974,7 +19974,7 @@
         <v>144</v>
       </c>
       <c r="F43" s="2">
-        <v>9827</v>
+        <v>9539</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>10</v>
@@ -19997,7 +19997,7 @@
         <v>144</v>
       </c>
       <c r="F44" s="2">
-        <v>10489</v>
+        <v>10201</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>10</v>
@@ -20020,7 +20020,7 @@
         <v>144</v>
       </c>
       <c r="F45" s="2">
-        <v>10890</v>
+        <v>10602</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>10</v>
@@ -20043,7 +20043,7 @@
         <v>144</v>
       </c>
       <c r="F46" s="2">
-        <v>8851</v>
+        <v>8563</v>
       </c>
       <c r="G46" s="3" t="s">
         <v>10</v>
@@ -20066,7 +20066,7 @@
         <v>144</v>
       </c>
       <c r="F47" s="2">
-        <v>4006</v>
+        <v>3286</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>10</v>
@@ -20089,7 +20089,7 @@
         <v>144</v>
       </c>
       <c r="F48" s="2">
-        <v>10132</v>
+        <v>9412</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>10</v>
@@ -20112,7 +20112,7 @@
         <v>144</v>
       </c>
       <c r="F49" s="2">
-        <v>15461</v>
+        <v>15029</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>10</v>
@@ -20135,7 +20135,7 @@
         <v>144</v>
       </c>
       <c r="F50" s="2">
-        <v>5608</v>
+        <v>5176</v>
       </c>
       <c r="G50" s="3" t="s">
         <v>10</v>
@@ -20158,7 +20158,7 @@
         <v>144</v>
       </c>
       <c r="F51" s="2">
-        <v>5079</v>
+        <v>4215</v>
       </c>
       <c r="G51" s="3" t="s">
         <v>10</v>
@@ -20181,7 +20181,7 @@
         <v>144</v>
       </c>
       <c r="F52" s="2">
-        <v>6454</v>
+        <v>5734</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>10</v>
@@ -20204,7 +20204,7 @@
         <v>144</v>
       </c>
       <c r="F53" s="2">
-        <v>6289</v>
+        <v>6001</v>
       </c>
       <c r="G53" s="3" t="s">
         <v>10</v>
@@ -20226,11 +20226,11 @@
       <c r="E54">
         <v>144</v>
       </c>
-      <c r="F54" s="6">
-        <v>432</v>
-      </c>
-      <c r="G54" s="7" t="s">
-        <v>49</v>
+      <c r="F54" s="4">
+        <v>0</v>
+      </c>
+      <c r="G54" s="5" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
@@ -20273,7 +20273,7 @@
         <v>144</v>
       </c>
       <c r="F56" s="6">
-        <v>265</v>
+        <v>121</v>
       </c>
       <c r="G56" s="7" t="s">
         <v>49</v>
@@ -20388,7 +20388,7 @@
         <v>96</v>
       </c>
       <c r="F61" s="2">
-        <v>3245</v>
+        <v>3053</v>
       </c>
       <c r="G61" s="3" t="s">
         <v>10</v>
@@ -20434,7 +20434,7 @@
         <v>120</v>
       </c>
       <c r="F63" s="2">
-        <v>9041</v>
+        <v>8681</v>
       </c>
       <c r="G63" s="3" t="s">
         <v>10</v>
@@ -20457,7 +20457,7 @@
         <v>120</v>
       </c>
       <c r="F64" s="2">
-        <v>7340</v>
+        <v>6980</v>
       </c>
       <c r="G64" s="3" t="s">
         <v>10</v>
@@ -21259,7 +21259,7 @@
         <v>72</v>
       </c>
       <c r="F2" s="2">
-        <v>120032</v>
+        <v>119312</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -21282,7 +21282,7 @@
         <v>72</v>
       </c>
       <c r="F3" s="2">
-        <v>212042</v>
+        <v>207042</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -21394,7 +21394,7 @@
         <v>12</v>
       </c>
       <c r="F2" s="2">
-        <v>1170</v>
+        <v>1146</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -21417,7 +21417,7 @@
         <v>12</v>
       </c>
       <c r="F3" s="2">
-        <v>1329</v>
+        <v>1305</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -21463,7 +21463,7 @@
         <v>12</v>
       </c>
       <c r="F5" s="2">
-        <v>857</v>
+        <v>737</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -21578,7 +21578,7 @@
         <v>48</v>
       </c>
       <c r="F10" s="2">
-        <v>2084</v>
+        <v>2036</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>10</v>
@@ -21601,7 +21601,7 @@
         <v>48</v>
       </c>
       <c r="F11" s="2">
-        <v>2119</v>
+        <v>2071</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>10</v>
@@ -21624,7 +21624,7 @@
         <v>48</v>
       </c>
       <c r="F12" s="2">
-        <v>2795</v>
+        <v>2747</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>10</v>
@@ -21647,7 +21647,7 @@
         <v>48</v>
       </c>
       <c r="F13" s="2">
-        <v>1630</v>
+        <v>1582</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>10</v>
@@ -21808,7 +21808,7 @@
         <v>24</v>
       </c>
       <c r="F20" s="2">
-        <v>1202</v>
+        <v>1154</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>10</v>
@@ -21831,7 +21831,7 @@
         <v>24</v>
       </c>
       <c r="F21" s="2">
-        <v>1344</v>
+        <v>1296</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>10</v>
@@ -21854,7 +21854,7 @@
         <v>24</v>
       </c>
       <c r="F22" s="2">
-        <v>1112</v>
+        <v>1064</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>10</v>
@@ -21877,7 +21877,7 @@
         <v>24</v>
       </c>
       <c r="F23" s="2">
-        <v>1048</v>
+        <v>1000</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>10</v>
@@ -22061,7 +22061,7 @@
         <v>12</v>
       </c>
       <c r="F31" s="2">
-        <v>613</v>
+        <v>553</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>10</v>
@@ -22219,7 +22219,7 @@
         <v>288</v>
       </c>
       <c r="F5" s="2">
-        <v>65501</v>
+        <v>62141</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -22242,7 +22242,7 @@
         <v>384</v>
       </c>
       <c r="F6" s="2">
-        <v>94120</v>
+        <v>92200</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>10</v>
@@ -22265,7 +22265,7 @@
         <v>384</v>
       </c>
       <c r="F7" s="2">
-        <v>57680</v>
+        <v>56528</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>10</v>
@@ -22380,7 +22380,7 @@
         <v>192</v>
       </c>
       <c r="F12" s="2">
-        <v>34134</v>
+        <v>30294</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>10</v>
@@ -22403,7 +22403,7 @@
         <v>576</v>
       </c>
       <c r="F13" s="2">
-        <v>91168</v>
+        <v>90016</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>10</v>
@@ -22426,7 +22426,7 @@
         <v>12</v>
       </c>
       <c r="F14" s="2">
-        <v>82069</v>
+        <v>79669</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>10</v>
@@ -22699,7 +22699,7 @@
         <v>500</v>
       </c>
       <c r="F3" s="2">
-        <v>9965</v>
+        <v>6965</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -22814,7 +22814,7 @@
         <v>400</v>
       </c>
       <c r="F8" s="2">
-        <v>16723</v>
+        <v>16323</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>10</v>
@@ -22837,7 +22837,7 @@
         <v>200</v>
       </c>
       <c r="F9" s="2">
-        <v>34772</v>
+        <v>33772</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>10</v>
@@ -22952,7 +22952,7 @@
         <v>200</v>
       </c>
       <c r="F14" s="2">
-        <v>1904</v>
+        <v>1504</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>10</v>
@@ -22997,11 +22997,11 @@
       <c r="E16">
         <v>200</v>
       </c>
-      <c r="F16" s="2">
-        <v>2347</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>10</v>
+      <c r="F16" s="6">
+        <v>347</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">

--- a/frontend/public/reports/StockPulse_ESCOLAR.xlsx
+++ b/frontend/public/reports/StockPulse_ESCOLAR.xlsx
@@ -6695,7 +6695,7 @@
         <v>25</v>
       </c>
       <c r="F2" s="2">
-        <v>71888</v>
+        <v>71588</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -6718,7 +6718,7 @@
         <v>50</v>
       </c>
       <c r="F3" s="2">
-        <v>229877</v>
+        <v>229477</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -6833,7 +6833,7 @@
         <v>48</v>
       </c>
       <c r="F8" s="2">
-        <v>68748</v>
+        <v>68700</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>10</v>
@@ -6856,7 +6856,7 @@
         <v>48</v>
       </c>
       <c r="F9" s="2">
-        <v>83713</v>
+        <v>83665</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>10</v>
@@ -6902,7 +6902,7 @@
         <v>36</v>
       </c>
       <c r="F11" s="2">
-        <v>27213</v>
+        <v>27141</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>10</v>
@@ -6925,7 +6925,7 @@
         <v>25</v>
       </c>
       <c r="F12" s="2">
-        <v>18203</v>
+        <v>18153</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>10</v>
@@ -6948,7 +6948,7 @@
         <v>50</v>
       </c>
       <c r="F13" s="2">
-        <v>117627</v>
+        <v>117527</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>10</v>
@@ -7497,7 +7497,7 @@
         <v>500</v>
       </c>
       <c r="F22" s="2">
-        <v>22084</v>
+        <v>21084</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>10</v>
@@ -7589,7 +7589,7 @@
         <v>120</v>
       </c>
       <c r="F26" s="2">
-        <v>2864</v>
+        <v>2840</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>10</v>
@@ -7839,7 +7839,7 @@
         <v>50</v>
       </c>
       <c r="F5" s="2">
-        <v>15754</v>
+        <v>15604</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -7885,7 +7885,7 @@
         <v>50</v>
       </c>
       <c r="F7" s="2">
-        <v>6939</v>
+        <v>6914</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>10</v>
@@ -7931,7 +7931,7 @@
         <v>50</v>
       </c>
       <c r="F9" s="2">
-        <v>3493</v>
+        <v>3468</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>10</v>
@@ -7954,7 +7954,7 @@
         <v>50</v>
       </c>
       <c r="F10" s="2">
-        <v>13654</v>
+        <v>13629</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>10</v>
@@ -7977,7 +7977,7 @@
         <v>50</v>
       </c>
       <c r="F11" s="2">
-        <v>4960</v>
+        <v>4935</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>10</v>
@@ -8000,7 +8000,7 @@
         <v>50</v>
       </c>
       <c r="F12" s="2">
-        <v>2859</v>
+        <v>2834</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>10</v>
@@ -8023,7 +8023,7 @@
         <v>50</v>
       </c>
       <c r="F13" s="2">
-        <v>4325</v>
+        <v>4300</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>10</v>
@@ -8045,11 +8045,11 @@
       <c r="E14">
         <v>50</v>
       </c>
-      <c r="F14" s="6">
-        <v>21</v>
-      </c>
-      <c r="G14" s="7" t="s">
-        <v>49</v>
+      <c r="F14" s="4">
+        <v>0</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -8092,7 +8092,7 @@
         <v>50</v>
       </c>
       <c r="F16" s="2">
-        <v>4892</v>
+        <v>4867</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>10</v>
@@ -8115,7 +8115,7 @@
         <v>50</v>
       </c>
       <c r="F17" s="2">
-        <v>7882</v>
+        <v>7857</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>10</v>
@@ -8138,7 +8138,7 @@
         <v>50</v>
       </c>
       <c r="F18" s="2">
-        <v>15119</v>
+        <v>15094</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>10</v>
@@ -8161,7 +8161,7 @@
         <v>50</v>
       </c>
       <c r="F19" s="2">
-        <v>1897</v>
+        <v>1872</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>10</v>
@@ -8207,7 +8207,7 @@
         <v>50</v>
       </c>
       <c r="F21" s="6">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="G21" s="7" t="s">
         <v>49</v>
@@ -8230,7 +8230,7 @@
         <v>50</v>
       </c>
       <c r="F22" s="2">
-        <v>493</v>
+        <v>468</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>10</v>
@@ -9311,7 +9311,7 @@
         <v>100</v>
       </c>
       <c r="F69" s="2">
-        <v>41458</v>
+        <v>41408</v>
       </c>
       <c r="G69" s="3" t="s">
         <v>10</v>
@@ -9495,7 +9495,7 @@
         <v>100</v>
       </c>
       <c r="F77" s="2">
-        <v>42324</v>
+        <v>42274</v>
       </c>
       <c r="G77" s="3" t="s">
         <v>10</v>
@@ -9518,7 +9518,7 @@
         <v>100</v>
       </c>
       <c r="F78" s="2">
-        <v>43284</v>
+        <v>43234</v>
       </c>
       <c r="G78" s="3" t="s">
         <v>10</v>
@@ -10461,7 +10461,7 @@
         <v>24</v>
       </c>
       <c r="F119" s="2">
-        <v>22716</v>
+        <v>22476</v>
       </c>
       <c r="G119" s="3" t="s">
         <v>10</v>
@@ -13589,7 +13589,7 @@
         <v>100</v>
       </c>
       <c r="F255" s="2">
-        <v>211687</v>
+        <v>211487</v>
       </c>
       <c r="G255" s="3" t="s">
         <v>10</v>
@@ -14253,7 +14253,7 @@
         <v>72</v>
       </c>
       <c r="F17" s="2">
-        <v>95653</v>
+        <v>95509</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>10</v>
@@ -14460,7 +14460,7 @@
         <v>60</v>
       </c>
       <c r="F26" s="2">
-        <v>32313</v>
+        <v>32301</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>10</v>
@@ -17631,7 +17631,7 @@
         <v>576</v>
       </c>
       <c r="F86" s="2">
-        <v>19868</v>
+        <v>19832</v>
       </c>
       <c r="G86" s="3" t="s">
         <v>10</v>
@@ -19261,7 +19261,7 @@
         <v>36</v>
       </c>
       <c r="F12" s="2">
-        <v>3709</v>
+        <v>3703</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>10</v>
@@ -19767,7 +19767,7 @@
         <v>120</v>
       </c>
       <c r="F34" s="2">
-        <v>47264</v>
+        <v>47204</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>10</v>
@@ -19813,7 +19813,7 @@
         <v>120</v>
       </c>
       <c r="F36" s="2">
-        <v>26255</v>
+        <v>26195</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>10</v>
@@ -19836,7 +19836,7 @@
         <v>120</v>
       </c>
       <c r="F37" s="2">
-        <v>7090</v>
+        <v>7030</v>
       </c>
       <c r="G37" s="3" t="s">
         <v>10</v>
@@ -19928,7 +19928,7 @@
         <v>144</v>
       </c>
       <c r="F41" s="2">
-        <v>6242</v>
+        <v>6170</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>10</v>
@@ -20365,7 +20365,7 @@
         <v>144</v>
       </c>
       <c r="F60" s="2">
-        <v>3866</v>
+        <v>3830</v>
       </c>
       <c r="G60" s="3" t="s">
         <v>10</v>
@@ -21923,7 +21923,7 @@
         <v>24</v>
       </c>
       <c r="F25" s="2">
-        <v>235</v>
+        <v>211</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>10</v>
@@ -22426,7 +22426,7 @@
         <v>12</v>
       </c>
       <c r="F14" s="2">
-        <v>79669</v>
+        <v>79549</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>10</v>
@@ -22676,7 +22676,7 @@
         <v>1000</v>
       </c>
       <c r="F2" s="6">
-        <v>3238</v>
+        <v>3088</v>
       </c>
       <c r="G2" s="7" t="s">
         <v>49</v>
@@ -22699,7 +22699,7 @@
         <v>500</v>
       </c>
       <c r="F3" s="2">
-        <v>6965</v>
+        <v>8815</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -22814,7 +22814,7 @@
         <v>400</v>
       </c>
       <c r="F8" s="2">
-        <v>16323</v>
+        <v>16273</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>10</v>
@@ -22837,7 +22837,7 @@
         <v>200</v>
       </c>
       <c r="F9" s="2">
-        <v>33772</v>
+        <v>33722</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>10</v>

--- a/frontend/public/reports/StockPulse_ESCOLAR.xlsx
+++ b/frontend/public/reports/StockPulse_ESCOLAR.xlsx
@@ -6718,7 +6718,7 @@
         <v>50</v>
       </c>
       <c r="F3" s="2">
-        <v>229477</v>
+        <v>226977</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -6810,7 +6810,7 @@
         <v>25</v>
       </c>
       <c r="F7" s="2">
-        <v>6425</v>
+        <v>5675</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>10</v>
@@ -6925,7 +6925,7 @@
         <v>25</v>
       </c>
       <c r="F12" s="2">
-        <v>18153</v>
+        <v>15778</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>10</v>
@@ -7931,7 +7931,7 @@
         <v>50</v>
       </c>
       <c r="F9" s="2">
-        <v>3468</v>
+        <v>3168</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>10</v>
@@ -8068,11 +8068,11 @@
       <c r="E15">
         <v>50</v>
       </c>
-      <c r="F15" s="4">
-        <v>0</v>
-      </c>
-      <c r="G15" s="5" t="s">
-        <v>19</v>
+      <c r="F15" s="6">
+        <v>5</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -10461,7 +10461,7 @@
         <v>24</v>
       </c>
       <c r="F119" s="2">
-        <v>22476</v>
+        <v>17391</v>
       </c>
       <c r="G119" s="3" t="s">
         <v>10</v>
@@ -14046,7 +14046,7 @@
         <v>72</v>
       </c>
       <c r="F8" s="2">
-        <v>14495</v>
+        <v>14493</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>10</v>
@@ -14253,7 +14253,7 @@
         <v>72</v>
       </c>
       <c r="F17" s="2">
-        <v>95509</v>
+        <v>95221</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>10</v>
@@ -14299,7 +14299,7 @@
         <v>36</v>
       </c>
       <c r="F19" s="2">
-        <v>4991</v>
+        <v>4989</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>10</v>
@@ -14437,7 +14437,7 @@
         <v>120</v>
       </c>
       <c r="F25" s="2">
-        <v>18308</v>
+        <v>17948</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>10</v>
@@ -15929,7 +15929,7 @@
         <v>144</v>
       </c>
       <c r="F12" s="2">
-        <v>11851</v>
+        <v>11850</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>10</v>
@@ -16849,7 +16849,7 @@
         <v>144</v>
       </c>
       <c r="F52" s="2">
-        <v>6779</v>
+        <v>6491</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>10</v>
@@ -17148,7 +17148,7 @@
         <v>200</v>
       </c>
       <c r="F65" s="2">
-        <v>4906</v>
+        <v>3046</v>
       </c>
       <c r="G65" s="3" t="s">
         <v>10</v>
@@ -17171,7 +17171,7 @@
         <v>200</v>
       </c>
       <c r="F66" s="2">
-        <v>7347</v>
+        <v>5657</v>
       </c>
       <c r="G66" s="3" t="s">
         <v>10</v>
@@ -17194,7 +17194,7 @@
         <v>200</v>
       </c>
       <c r="F67" s="2">
-        <v>33638</v>
+        <v>32678</v>
       </c>
       <c r="G67" s="3" t="s">
         <v>10</v>
@@ -17263,7 +17263,7 @@
         <v>200</v>
       </c>
       <c r="F70" s="2">
-        <v>8581</v>
+        <v>7171</v>
       </c>
       <c r="G70" s="3" t="s">
         <v>10</v>
@@ -17285,11 +17285,11 @@
       <c r="E71">
         <v>200</v>
       </c>
-      <c r="F71" s="2">
-        <v>1246</v>
-      </c>
-      <c r="G71" s="3" t="s">
-        <v>10</v>
+      <c r="F71" s="6">
+        <v>966</v>
+      </c>
+      <c r="G71" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
@@ -17768,11 +17768,11 @@
       <c r="E92">
         <v>576</v>
       </c>
-      <c r="F92" s="2">
-        <v>4231</v>
-      </c>
-      <c r="G92" s="3" t="s">
-        <v>10</v>
+      <c r="F92" s="6">
+        <v>2731</v>
+      </c>
+      <c r="G92" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
@@ -19077,7 +19077,7 @@
         <v>50</v>
       </c>
       <c r="F4" s="2">
-        <v>11181</v>
+        <v>11081</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>10</v>
@@ -19537,7 +19537,7 @@
         <v>60</v>
       </c>
       <c r="F24" s="2">
-        <v>3513</v>
+        <v>3453</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>10</v>
@@ -19974,7 +19974,7 @@
         <v>144</v>
       </c>
       <c r="F43" s="2">
-        <v>9539</v>
+        <v>9251</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>10</v>
@@ -19997,7 +19997,7 @@
         <v>144</v>
       </c>
       <c r="F44" s="2">
-        <v>10201</v>
+        <v>9913</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>10</v>
@@ -20020,7 +20020,7 @@
         <v>144</v>
       </c>
       <c r="F45" s="2">
-        <v>10602</v>
+        <v>10314</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>10</v>
@@ -20043,7 +20043,7 @@
         <v>144</v>
       </c>
       <c r="F46" s="2">
-        <v>8563</v>
+        <v>8274</v>
       </c>
       <c r="G46" s="3" t="s">
         <v>10</v>
@@ -20066,7 +20066,7 @@
         <v>144</v>
       </c>
       <c r="F47" s="2">
-        <v>3286</v>
+        <v>3285</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>10</v>
@@ -21147,7 +21147,7 @@
         <v>144</v>
       </c>
       <c r="F94" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G94" s="7" t="s">
         <v>49</v>
@@ -21282,7 +21282,7 @@
         <v>72</v>
       </c>
       <c r="F3" s="2">
-        <v>207042</v>
+        <v>206682</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -22173,7 +22173,7 @@
         <v>384</v>
       </c>
       <c r="F3" s="2">
-        <v>34348</v>
+        <v>33580</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>

--- a/frontend/public/reports/StockPulse_ESCOLAR.xlsx
+++ b/frontend/public/reports/StockPulse_ESCOLAR.xlsx
@@ -6833,7 +6833,7 @@
         <v>48</v>
       </c>
       <c r="F8" s="2">
-        <v>68700</v>
+        <v>68604</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>10</v>
@@ -7497,7 +7497,7 @@
         <v>500</v>
       </c>
       <c r="F22" s="2">
-        <v>21084</v>
+        <v>18584</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>10</v>
@@ -7885,7 +7885,7 @@
         <v>50</v>
       </c>
       <c r="F7" s="2">
-        <v>6914</v>
+        <v>6864</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>10</v>
@@ -7931,7 +7931,7 @@
         <v>50</v>
       </c>
       <c r="F9" s="2">
-        <v>3168</v>
+        <v>3118</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>10</v>
@@ -7954,7 +7954,7 @@
         <v>50</v>
       </c>
       <c r="F10" s="2">
-        <v>13629</v>
+        <v>13579</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>10</v>
@@ -8115,7 +8115,7 @@
         <v>50</v>
       </c>
       <c r="F17" s="2">
-        <v>7857</v>
+        <v>7807</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>10</v>
@@ -8230,7 +8230,7 @@
         <v>50</v>
       </c>
       <c r="F22" s="2">
-        <v>468</v>
+        <v>418</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>10</v>
@@ -9288,7 +9288,7 @@
         <v>100</v>
       </c>
       <c r="F68" s="2">
-        <v>38116</v>
+        <v>37916</v>
       </c>
       <c r="G68" s="3" t="s">
         <v>10</v>
@@ -9311,7 +9311,7 @@
         <v>100</v>
       </c>
       <c r="F69" s="2">
-        <v>41408</v>
+        <v>41208</v>
       </c>
       <c r="G69" s="3" t="s">
         <v>10</v>
@@ -9356,11 +9356,11 @@
       <c r="E71">
         <v>100</v>
       </c>
-      <c r="F71" s="6">
-        <v>100</v>
-      </c>
-      <c r="G71" s="7" t="s">
-        <v>49</v>
+      <c r="F71" s="4">
+        <v>0</v>
+      </c>
+      <c r="G71" s="5" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
@@ -10668,7 +10668,7 @@
         <v>24</v>
       </c>
       <c r="F128" s="2">
-        <v>5534</v>
+        <v>5486</v>
       </c>
       <c r="G128" s="3" t="s">
         <v>10</v>
@@ -10691,7 +10691,7 @@
         <v>24</v>
       </c>
       <c r="F129" s="2">
-        <v>8160</v>
+        <v>8112</v>
       </c>
       <c r="G129" s="3" t="s">
         <v>10</v>
@@ -10714,7 +10714,7 @@
         <v>24</v>
       </c>
       <c r="F130" s="2">
-        <v>15659</v>
+        <v>15611</v>
       </c>
       <c r="G130" s="3" t="s">
         <v>10</v>
@@ -10737,7 +10737,7 @@
         <v>24</v>
       </c>
       <c r="F131" s="2">
-        <v>9762</v>
+        <v>9714</v>
       </c>
       <c r="G131" s="3" t="s">
         <v>10</v>
@@ -13014,7 +13014,7 @@
         <v>5</v>
       </c>
       <c r="F230" s="2">
-        <v>917</v>
+        <v>857</v>
       </c>
       <c r="G230" s="3" t="s">
         <v>10</v>
@@ -13060,7 +13060,7 @@
         <v>5</v>
       </c>
       <c r="F232" s="2">
-        <v>262</v>
+        <v>232</v>
       </c>
       <c r="G232" s="3" t="s">
         <v>10</v>
@@ -13105,11 +13105,11 @@
       <c r="E234">
         <v>5</v>
       </c>
-      <c r="F234" s="2">
-        <v>72</v>
-      </c>
-      <c r="G234" s="3" t="s">
-        <v>10</v>
+      <c r="F234" s="6">
+        <v>22</v>
+      </c>
+      <c r="G234" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.25">
@@ -13129,7 +13129,7 @@
         <v>5</v>
       </c>
       <c r="F235" s="2">
-        <v>361</v>
+        <v>336</v>
       </c>
       <c r="G235" s="3" t="s">
         <v>10</v>
@@ -13152,7 +13152,7 @@
         <v>5</v>
       </c>
       <c r="F236" s="2">
-        <v>257</v>
+        <v>217</v>
       </c>
       <c r="G236" s="3" t="s">
         <v>10</v>
@@ -13175,7 +13175,7 @@
         <v>5</v>
       </c>
       <c r="F237" s="2">
-        <v>257</v>
+        <v>212</v>
       </c>
       <c r="G237" s="3" t="s">
         <v>10</v>
@@ -13198,7 +13198,7 @@
         <v>5</v>
       </c>
       <c r="F238" s="2">
-        <v>231</v>
+        <v>181</v>
       </c>
       <c r="G238" s="3" t="s">
         <v>10</v>
@@ -13221,7 +13221,7 @@
         <v>5</v>
       </c>
       <c r="F239" s="2">
-        <v>277</v>
+        <v>247</v>
       </c>
       <c r="G239" s="3" t="s">
         <v>10</v>
@@ -13267,7 +13267,7 @@
         <v>5</v>
       </c>
       <c r="F241" s="2">
-        <v>1695</v>
+        <v>1515</v>
       </c>
       <c r="G241" s="3" t="s">
         <v>10</v>
@@ -13382,7 +13382,7 @@
         <v>5</v>
       </c>
       <c r="F246" s="2">
-        <v>236</v>
+        <v>191</v>
       </c>
       <c r="G246" s="3" t="s">
         <v>10</v>
@@ -13405,7 +13405,7 @@
         <v>5</v>
       </c>
       <c r="F247" s="2">
-        <v>382</v>
+        <v>352</v>
       </c>
       <c r="G247" s="3" t="s">
         <v>10</v>
@@ -14115,7 +14115,7 @@
         <v>144</v>
       </c>
       <c r="F11" s="2">
-        <v>52785</v>
+        <v>52784</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>10</v>
@@ -14253,7 +14253,7 @@
         <v>72</v>
       </c>
       <c r="F17" s="2">
-        <v>95221</v>
+        <v>94973</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>10</v>
@@ -14391,7 +14391,7 @@
         <v>60</v>
       </c>
       <c r="F23" s="2">
-        <v>12968</v>
+        <v>12967</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>10</v>
@@ -14529,7 +14529,7 @@
         <v>576</v>
       </c>
       <c r="F29" s="2">
-        <v>51222</v>
+        <v>51102</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>10</v>
@@ -14943,7 +14943,7 @@
         <v>288</v>
       </c>
       <c r="F47" s="2">
-        <v>8672</v>
+        <v>8472</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>10</v>
@@ -15311,7 +15311,7 @@
         <v>12</v>
       </c>
       <c r="F63" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G63" s="7" t="s">
         <v>49</v>
@@ -16021,7 +16021,7 @@
         <v>96</v>
       </c>
       <c r="F16" s="2">
-        <v>9579</v>
+        <v>9479</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>10</v>
@@ -16044,7 +16044,7 @@
         <v>192</v>
       </c>
       <c r="F17" s="2">
-        <v>14522</v>
+        <v>14322</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>10</v>
@@ -16136,7 +16136,7 @@
         <v>192</v>
       </c>
       <c r="F21" s="2">
-        <v>9266</v>
+        <v>9265</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>10</v>
@@ -16228,7 +16228,7 @@
         <v>48</v>
       </c>
       <c r="F25" s="2">
-        <v>3746</v>
+        <v>3650</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>10</v>
@@ -16320,7 +16320,7 @@
         <v>192</v>
       </c>
       <c r="F29" s="2">
-        <v>13781</v>
+        <v>13681</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>10</v>
@@ -16343,7 +16343,7 @@
         <v>192</v>
       </c>
       <c r="F30" s="2">
-        <v>30886</v>
+        <v>30786</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>10</v>
@@ -16872,7 +16872,7 @@
         <v>96</v>
       </c>
       <c r="F53" s="2">
-        <v>14109</v>
+        <v>14009</v>
       </c>
       <c r="G53" s="3" t="s">
         <v>10</v>
@@ -17539,7 +17539,7 @@
         <v>1152</v>
       </c>
       <c r="F82" s="2">
-        <v>56162</v>
+        <v>55802</v>
       </c>
       <c r="G82" s="3" t="s">
         <v>10</v>
@@ -17631,7 +17631,7 @@
         <v>576</v>
       </c>
       <c r="F86" s="2">
-        <v>19832</v>
+        <v>19831</v>
       </c>
       <c r="G86" s="3" t="s">
         <v>10</v>
@@ -17769,7 +17769,7 @@
         <v>576</v>
       </c>
       <c r="F92" s="6">
-        <v>2731</v>
+        <v>1231</v>
       </c>
       <c r="G92" s="7" t="s">
         <v>49</v>
@@ -17861,7 +17861,7 @@
         <v>144</v>
       </c>
       <c r="F96" s="2">
-        <v>190504</v>
+        <v>186903</v>
       </c>
       <c r="G96" s="3" t="s">
         <v>10</v>
@@ -19445,7 +19445,7 @@
         <v>36</v>
       </c>
       <c r="F20" s="2">
-        <v>5384</v>
+        <v>5348</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>10</v>
@@ -19491,7 +19491,7 @@
         <v>36</v>
       </c>
       <c r="F22" s="2">
-        <v>15898</v>
+        <v>15798</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>10</v>
@@ -19698,7 +19698,7 @@
         <v>144</v>
       </c>
       <c r="F31" s="2">
-        <v>138643</v>
+        <v>137620</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>10</v>
@@ -19859,7 +19859,7 @@
         <v>120</v>
       </c>
       <c r="F38" s="2">
-        <v>100416</v>
+        <v>99906</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>10</v>
@@ -19997,7 +19997,7 @@
         <v>144</v>
       </c>
       <c r="F44" s="2">
-        <v>9913</v>
+        <v>9912</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>10</v>
@@ -20871,7 +20871,7 @@
         <v>144</v>
       </c>
       <c r="F82" s="2">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="G82" s="3" t="s">
         <v>10</v>
@@ -22426,7 +22426,7 @@
         <v>12</v>
       </c>
       <c r="F14" s="2">
-        <v>79549</v>
+        <v>79309</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>10</v>
@@ -22837,7 +22837,7 @@
         <v>200</v>
       </c>
       <c r="F9" s="2">
-        <v>33722</v>
+        <v>33522</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>10</v>

--- a/frontend/public/reports/StockPulse_ESCOLAR.xlsx
+++ b/frontend/public/reports/StockPulse_ESCOLAR.xlsx
@@ -6695,7 +6695,7 @@
         <v>25</v>
       </c>
       <c r="F2" s="2">
-        <v>71588</v>
+        <v>71338</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -6718,7 +6718,7 @@
         <v>50</v>
       </c>
       <c r="F3" s="2">
-        <v>226977</v>
+        <v>226677</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -7474,7 +7474,7 @@
         <v>500</v>
       </c>
       <c r="F21" s="2">
-        <v>45255</v>
+        <v>45254</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>10</v>
@@ -8299,7 +8299,7 @@
         <v>50</v>
       </c>
       <c r="F25" s="2">
-        <v>23011</v>
+        <v>22981</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>10</v>
@@ -11450,7 +11450,7 @@
         <v>24</v>
       </c>
       <c r="F162" s="2">
-        <v>1747</v>
+        <v>1735</v>
       </c>
       <c r="G162" s="3" t="s">
         <v>10</v>
@@ -11496,7 +11496,7 @@
         <v>24</v>
       </c>
       <c r="F164" s="2">
-        <v>948</v>
+        <v>942</v>
       </c>
       <c r="G164" s="3" t="s">
         <v>10</v>
@@ -13977,7 +13977,7 @@
         <v>24</v>
       </c>
       <c r="F5" s="2">
-        <v>2259</v>
+        <v>2307</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -14000,7 +14000,7 @@
         <v>18</v>
       </c>
       <c r="F6" s="2">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>10</v>
@@ -14023,7 +14023,7 @@
         <v>144</v>
       </c>
       <c r="F7" s="2">
-        <v>103185</v>
+        <v>103184</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>10</v>
@@ -14115,7 +14115,7 @@
         <v>144</v>
       </c>
       <c r="F11" s="2">
-        <v>52784</v>
+        <v>52782</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>10</v>
@@ -14253,7 +14253,7 @@
         <v>72</v>
       </c>
       <c r="F17" s="2">
-        <v>94973</v>
+        <v>94919</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>10</v>
@@ -14483,7 +14483,7 @@
         <v>60</v>
       </c>
       <c r="F27" s="2">
-        <v>71146</v>
+        <v>71144</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>10</v>
@@ -14966,7 +14966,7 @@
         <v>144</v>
       </c>
       <c r="F48" s="2">
-        <v>46936</v>
+        <v>46934</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>10</v>
@@ -14989,7 +14989,7 @@
         <v>36</v>
       </c>
       <c r="F49" s="2">
-        <v>37845</v>
+        <v>37843</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>10</v>
@@ -15334,7 +15334,7 @@
         <v>12</v>
       </c>
       <c r="F64" s="6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G64" s="7" t="s">
         <v>49</v>
@@ -15699,7 +15699,7 @@
         <v>144</v>
       </c>
       <c r="F2" s="2">
-        <v>73106</v>
+        <v>73105</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -15791,7 +15791,7 @@
         <v>144</v>
       </c>
       <c r="F6" s="2">
-        <v>2640</v>
+        <v>2638</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>10</v>
@@ -15975,7 +15975,7 @@
         <v>96</v>
       </c>
       <c r="F14" s="2">
-        <v>9249</v>
+        <v>9248</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>10</v>
@@ -15998,7 +15998,7 @@
         <v>96</v>
       </c>
       <c r="F15" s="2">
-        <v>7551</v>
+        <v>7550</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>10</v>
@@ -16228,7 +16228,7 @@
         <v>48</v>
       </c>
       <c r="F25" s="2">
-        <v>3650</v>
+        <v>3647</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>10</v>
@@ -16780,7 +16780,7 @@
         <v>96</v>
       </c>
       <c r="F49" s="2">
-        <v>12651</v>
+        <v>12650</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>10</v>
@@ -16849,7 +16849,7 @@
         <v>144</v>
       </c>
       <c r="F52" s="2">
-        <v>6491</v>
+        <v>6455</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>10</v>
@@ -16872,7 +16872,7 @@
         <v>96</v>
       </c>
       <c r="F53" s="2">
-        <v>14009</v>
+        <v>14008</v>
       </c>
       <c r="G53" s="3" t="s">
         <v>10</v>
@@ -16895,7 +16895,7 @@
         <v>96</v>
       </c>
       <c r="F54" s="2">
-        <v>7483</v>
+        <v>7482</v>
       </c>
       <c r="G54" s="3" t="s">
         <v>10</v>
@@ -17837,11 +17837,11 @@
       <c r="E95">
         <v>120</v>
       </c>
-      <c r="F95" s="4">
-        <v>0</v>
-      </c>
-      <c r="G95" s="5" t="s">
-        <v>19</v>
+      <c r="F95" s="6">
+        <v>3</v>
+      </c>
+      <c r="G95" s="7" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
@@ -17884,7 +17884,7 @@
         <v>288</v>
       </c>
       <c r="F97" s="2">
-        <v>25656</v>
+        <v>25654</v>
       </c>
       <c r="G97" s="3" t="s">
         <v>10</v>
@@ -19169,7 +19169,7 @@
         <v>144</v>
       </c>
       <c r="F8" s="2">
-        <v>17891</v>
+        <v>17890</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>10</v>
@@ -19744,7 +19744,7 @@
         <v>120</v>
       </c>
       <c r="F33" s="2">
-        <v>38192</v>
+        <v>38191</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>10</v>
@@ -19767,7 +19767,7 @@
         <v>120</v>
       </c>
       <c r="F34" s="2">
-        <v>47204</v>
+        <v>46104</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>10</v>
@@ -19859,7 +19859,7 @@
         <v>120</v>
       </c>
       <c r="F38" s="2">
-        <v>99906</v>
+        <v>99816</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>10</v>
@@ -20135,7 +20135,7 @@
         <v>144</v>
       </c>
       <c r="F50" s="2">
-        <v>5176</v>
+        <v>5174</v>
       </c>
       <c r="G50" s="3" t="s">
         <v>10</v>
@@ -20273,7 +20273,7 @@
         <v>144</v>
       </c>
       <c r="F56" s="6">
-        <v>121</v>
+        <v>145</v>
       </c>
       <c r="G56" s="7" t="s">
         <v>49</v>
@@ -20434,7 +20434,7 @@
         <v>120</v>
       </c>
       <c r="F63" s="2">
-        <v>8681</v>
+        <v>8680</v>
       </c>
       <c r="G63" s="3" t="s">
         <v>10</v>
@@ -20457,7 +20457,7 @@
         <v>120</v>
       </c>
       <c r="F64" s="2">
-        <v>6980</v>
+        <v>6979</v>
       </c>
       <c r="G64" s="3" t="s">
         <v>10</v>
@@ -20848,7 +20848,7 @@
         <v>144</v>
       </c>
       <c r="F81" s="6">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G81" s="7" t="s">
         <v>49</v>
@@ -21147,7 +21147,7 @@
         <v>144</v>
       </c>
       <c r="F94" s="6">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G94" s="7" t="s">
         <v>49</v>
@@ -21259,7 +21259,7 @@
         <v>72</v>
       </c>
       <c r="F2" s="2">
-        <v>119312</v>
+        <v>119309</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -21808,7 +21808,7 @@
         <v>24</v>
       </c>
       <c r="F20" s="2">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>10</v>
@@ -22288,7 +22288,7 @@
         <v>144</v>
       </c>
       <c r="F8" s="2">
-        <v>1979</v>
+        <v>1977</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>10</v>
@@ -22334,7 +22334,7 @@
         <v>36</v>
       </c>
       <c r="F10" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G10" s="7" t="s">
         <v>49</v>

--- a/frontend/public/reports/StockPulse_ESCOLAR.xlsx
+++ b/frontend/public/reports/StockPulse_ESCOLAR.xlsx
@@ -6718,7 +6718,7 @@
         <v>50</v>
       </c>
       <c r="F3" s="2">
-        <v>226677</v>
+        <v>226077</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -6741,7 +6741,7 @@
         <v>100</v>
       </c>
       <c r="F4" s="2">
-        <v>80312</v>
+        <v>80112</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>10</v>
@@ -6833,7 +6833,7 @@
         <v>48</v>
       </c>
       <c r="F8" s="2">
-        <v>68604</v>
+        <v>68599</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>10</v>
@@ -7862,7 +7862,7 @@
         <v>50</v>
       </c>
       <c r="F6" s="2">
-        <v>17813</v>
+        <v>17713</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>10</v>
@@ -10461,7 +10461,7 @@
         <v>24</v>
       </c>
       <c r="F119" s="2">
-        <v>17391</v>
+        <v>22791</v>
       </c>
       <c r="G119" s="3" t="s">
         <v>10</v>
@@ -11312,7 +11312,7 @@
         <v>6</v>
       </c>
       <c r="F156" s="2">
-        <v>900</v>
+        <v>870</v>
       </c>
       <c r="G156" s="3" t="s">
         <v>10</v>
@@ -11335,7 +11335,7 @@
         <v>6</v>
       </c>
       <c r="F157" s="2">
-        <v>179</v>
+        <v>119</v>
       </c>
       <c r="G157" s="3" t="s">
         <v>10</v>
@@ -14023,7 +14023,7 @@
         <v>144</v>
       </c>
       <c r="F7" s="2">
-        <v>103184</v>
+        <v>102896</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>10</v>
@@ -14138,7 +14138,7 @@
         <v>144</v>
       </c>
       <c r="F12" s="2">
-        <v>14383</v>
+        <v>14243</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>10</v>
@@ -14253,7 +14253,7 @@
         <v>72</v>
       </c>
       <c r="F17" s="2">
-        <v>94919</v>
+        <v>94853</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>10</v>
@@ -14989,7 +14989,7 @@
         <v>36</v>
       </c>
       <c r="F49" s="2">
-        <v>37843</v>
+        <v>37807</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>10</v>
@@ -15722,7 +15722,7 @@
         <v>144</v>
       </c>
       <c r="F3" s="2">
-        <v>37073</v>
+        <v>36593</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -16228,7 +16228,7 @@
         <v>48</v>
       </c>
       <c r="F25" s="2">
-        <v>3647</v>
+        <v>3503</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>10</v>
@@ -16251,7 +16251,7 @@
         <v>24</v>
       </c>
       <c r="F26" s="2">
-        <v>12943</v>
+        <v>12823</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>10</v>
@@ -22380,7 +22380,7 @@
         <v>192</v>
       </c>
       <c r="F12" s="2">
-        <v>30294</v>
+        <v>30102</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>10</v>
@@ -22426,7 +22426,7 @@
         <v>12</v>
       </c>
       <c r="F14" s="2">
-        <v>79309</v>
+        <v>78778</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>10</v>
@@ -22814,7 +22814,7 @@
         <v>400</v>
       </c>
       <c r="F8" s="2">
-        <v>16273</v>
+        <v>16023</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>10</v>

--- a/frontend/public/reports/StockPulse_ESCOLAR.xlsx
+++ b/frontend/public/reports/StockPulse_ESCOLAR.xlsx
@@ -6741,7 +6741,7 @@
         <v>100</v>
       </c>
       <c r="F4" s="2">
-        <v>80112</v>
+        <v>79612</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>10</v>
@@ -6833,7 +6833,7 @@
         <v>48</v>
       </c>
       <c r="F8" s="2">
-        <v>68599</v>
+        <v>68359</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>10</v>
@@ -6856,7 +6856,7 @@
         <v>48</v>
       </c>
       <c r="F9" s="2">
-        <v>83665</v>
+        <v>83425</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>10</v>
@@ -6925,7 +6925,7 @@
         <v>25</v>
       </c>
       <c r="F12" s="2">
-        <v>15378</v>
+        <v>15253</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>10</v>
@@ -7336,7 +7336,7 @@
         <v>100</v>
       </c>
       <c r="F15" s="2">
-        <v>38769</v>
+        <v>38369</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>10</v>
@@ -7839,7 +7839,7 @@
         <v>50</v>
       </c>
       <c r="F5" s="2">
-        <v>15604</v>
+        <v>15454</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -8276,7 +8276,7 @@
         <v>50</v>
       </c>
       <c r="F24" s="2">
-        <v>47692</v>
+        <v>49492</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>10</v>
@@ -8299,7 +8299,7 @@
         <v>50</v>
       </c>
       <c r="F25" s="2">
-        <v>22981</v>
+        <v>22731</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>10</v>
@@ -8322,7 +8322,7 @@
         <v>50</v>
       </c>
       <c r="F26" s="2">
-        <v>8903</v>
+        <v>8803</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>10</v>
@@ -8345,7 +8345,7 @@
         <v>50</v>
       </c>
       <c r="F27" s="2">
-        <v>6190</v>
+        <v>6090</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>10</v>
@@ -8368,7 +8368,7 @@
         <v>50</v>
       </c>
       <c r="F28" s="2">
-        <v>23250</v>
+        <v>23249</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>10</v>
@@ -8414,7 +8414,7 @@
         <v>50</v>
       </c>
       <c r="F30" s="2">
-        <v>9625</v>
+        <v>9525</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>10</v>
@@ -8437,7 +8437,7 @@
         <v>50</v>
       </c>
       <c r="F31" s="2">
-        <v>1199</v>
+        <v>1149</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>10</v>
@@ -8460,7 +8460,7 @@
         <v>50</v>
       </c>
       <c r="F32" s="2">
-        <v>5477</v>
+        <v>5427</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>10</v>
@@ -8506,7 +8506,7 @@
         <v>50</v>
       </c>
       <c r="F34" s="2">
-        <v>8399</v>
+        <v>8299</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>10</v>
@@ -8529,7 +8529,7 @@
         <v>50</v>
       </c>
       <c r="F35" s="2">
-        <v>18661</v>
+        <v>18611</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>10</v>
@@ -8598,7 +8598,7 @@
         <v>50</v>
       </c>
       <c r="F38" s="2">
-        <v>4261</v>
+        <v>4260</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>10</v>
@@ -8621,7 +8621,7 @@
         <v>50</v>
       </c>
       <c r="F39" s="2">
-        <v>2722</v>
+        <v>2622</v>
       </c>
       <c r="G39" s="3" t="s">
         <v>10</v>
@@ -10644,11 +10644,11 @@
       <c r="E127">
         <v>24</v>
       </c>
-      <c r="F127" s="6">
-        <v>56</v>
-      </c>
-      <c r="G127" s="7" t="s">
-        <v>49</v>
+      <c r="F127" s="2">
+        <v>176</v>
+      </c>
+      <c r="G127" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.25">
@@ -11174,7 +11174,7 @@
         <v>12</v>
       </c>
       <c r="F150" s="2">
-        <v>2559</v>
+        <v>2675</v>
       </c>
       <c r="G150" s="3" t="s">
         <v>10</v>
@@ -13589,7 +13589,7 @@
         <v>100</v>
       </c>
       <c r="F255" s="2">
-        <v>211487</v>
+        <v>211187</v>
       </c>
       <c r="G255" s="3" t="s">
         <v>10</v>
@@ -14023,7 +14023,7 @@
         <v>144</v>
       </c>
       <c r="F7" s="2">
-        <v>102896</v>
+        <v>102895</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>10</v>
@@ -14138,7 +14138,7 @@
         <v>144</v>
       </c>
       <c r="F12" s="2">
-        <v>13881</v>
+        <v>13737</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>10</v>
@@ -14253,7 +14253,7 @@
         <v>72</v>
       </c>
       <c r="F17" s="2">
-        <v>94832</v>
+        <v>94831</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>10</v>
@@ -14276,7 +14276,7 @@
         <v>72</v>
       </c>
       <c r="F18" s="2">
-        <v>6427</v>
+        <v>6403</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>10</v>
@@ -14483,7 +14483,7 @@
         <v>60</v>
       </c>
       <c r="F27" s="2">
-        <v>71144</v>
+        <v>70724</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>10</v>
@@ -14644,7 +14644,7 @@
         <v>576</v>
       </c>
       <c r="F34" s="2">
-        <v>48805</v>
+        <v>48565</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>10</v>
@@ -14782,7 +14782,7 @@
         <v>576</v>
       </c>
       <c r="F40" s="2">
-        <v>40056</v>
+        <v>39816</v>
       </c>
       <c r="G40" s="3" t="s">
         <v>10</v>
@@ -14874,7 +14874,7 @@
         <v>576</v>
       </c>
       <c r="F44" s="6">
-        <v>125</v>
+        <v>5</v>
       </c>
       <c r="G44" s="7" t="s">
         <v>49</v>
@@ -14989,7 +14989,7 @@
         <v>36</v>
       </c>
       <c r="F49" s="2">
-        <v>37374</v>
+        <v>37373</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>10</v>
@@ -17171,7 +17171,7 @@
         <v>200</v>
       </c>
       <c r="F66" s="2">
-        <v>5657</v>
+        <v>5457</v>
       </c>
       <c r="G66" s="3" t="s">
         <v>10</v>
@@ -17792,7 +17792,7 @@
         <v>576</v>
       </c>
       <c r="F93" s="2">
-        <v>14231</v>
+        <v>13655</v>
       </c>
       <c r="G93" s="3" t="s">
         <v>10</v>
@@ -19054,7 +19054,7 @@
         <v>50</v>
       </c>
       <c r="F3" s="2">
-        <v>2703</v>
+        <v>2653</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -19445,7 +19445,7 @@
         <v>36</v>
       </c>
       <c r="F20" s="2">
-        <v>5348</v>
+        <v>5312</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>10</v>
@@ -19583,7 +19583,7 @@
         <v>36</v>
       </c>
       <c r="F26" s="2">
-        <v>5313</v>
+        <v>5277</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>10</v>
@@ -19698,7 +19698,7 @@
         <v>144</v>
       </c>
       <c r="F31" s="2">
-        <v>137620</v>
+        <v>137044</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>10</v>
@@ -19744,7 +19744,7 @@
         <v>120</v>
       </c>
       <c r="F33" s="2">
-        <v>38071</v>
+        <v>37830</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>10</v>
@@ -19905,7 +19905,7 @@
         <v>120</v>
       </c>
       <c r="F40" s="2">
-        <v>888</v>
+        <v>768</v>
       </c>
       <c r="G40" s="3" t="s">
         <v>10</v>
@@ -19928,7 +19928,7 @@
         <v>144</v>
       </c>
       <c r="F41" s="2">
-        <v>6170</v>
+        <v>6134</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>10</v>
@@ -20181,7 +20181,7 @@
         <v>144</v>
       </c>
       <c r="F52" s="2">
-        <v>5734</v>
+        <v>5698</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>10</v>
@@ -20388,7 +20388,7 @@
         <v>96</v>
       </c>
       <c r="F61" s="2">
-        <v>3053</v>
+        <v>2957</v>
       </c>
       <c r="G61" s="3" t="s">
         <v>10</v>
@@ -21282,7 +21282,7 @@
         <v>72</v>
       </c>
       <c r="F3" s="2">
-        <v>206681</v>
+        <v>206536</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -22288,7 +22288,7 @@
         <v>144</v>
       </c>
       <c r="F8" s="2">
-        <v>1977</v>
+        <v>1976</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>10</v>
@@ -22745,7 +22745,7 @@
         <v>500</v>
       </c>
       <c r="F5" s="2">
-        <v>10493</v>
+        <v>10492</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>10</v>
@@ -22837,7 +22837,7 @@
         <v>200</v>
       </c>
       <c r="F9" s="2">
-        <v>33522</v>
+        <v>33221</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>10</v>
